--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/25,06,26 Останкино СЫР/Дв. 22.06.2026 Останкино Сыр Луганск (согласован).xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/25,06,26 Останкино СЫР/Дв. 22.06.2026 Останкино Сыр Луганск (согласован).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\Заказы на отправку и сортировку\Останкино\Останкино исходники\СЫРЫ\Луганск\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\25,06,26 Останкино СЫР\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DD20E6-D0D7-48E8-916A-A46F5C377D1D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D78B02-B5B1-4CA2-BE5C-9EAB28A11108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,18 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TDSheet!$A$8:$AB$57</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -290,9 +279,6 @@
     <t>7216 СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам. ОСТАНКИНО</t>
   </si>
   <si>
-    <t>итого</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -300,6 +286,9 @@
   </si>
   <si>
     <t>блины</t>
+  </si>
+  <si>
+    <t>заказ</t>
   </si>
 </sst>
 </file>
@@ -309,7 +298,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <name val="Arial"/>
@@ -341,6 +330,20 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -474,7 +477,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -488,7 +491,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -515,16 +517,23 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -544,7 +553,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="TDSheet"/>
@@ -3363,7 +3372,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="TDSheet"/>
@@ -3848,9 +3857,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3888,9 +3897,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3923,26 +3932,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3975,26 +3967,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4179,35 +4154,38 @@
     <col min="2" max="2" width="4.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" customWidth="1"/>
     <col min="4" max="7" width="8.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.5" style="5" customWidth="1"/>
-    <col min="11" max="11" width="2.6640625" style="5" customWidth="1"/>
-    <col min="12" max="12" width="9.5" style="5" customWidth="1"/>
-    <col min="13" max="13" width="6.83203125" style="5" customWidth="1"/>
-    <col min="14" max="14" width="9.5" style="5" customWidth="1"/>
-    <col min="15" max="15" width="8" style="5" customWidth="1"/>
-    <col min="16" max="16" width="8.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10" style="5" customWidth="1"/>
-    <col min="19" max="19" width="9.5" style="5" customWidth="1"/>
-    <col min="20" max="20" width="9.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="7.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.5" style="5" customWidth="1"/>
-    <col min="27" max="28" width="7.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="29" max="48" width="5.6640625" style="5" customWidth="1"/>
-    <col min="49" max="16384" width="18" style="5"/>
+    <col min="8" max="8" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5" customWidth="1"/>
+    <col min="11" max="11" width="2.6640625" customWidth="1"/>
+    <col min="12" max="12" width="9.5" customWidth="1"/>
+    <col min="13" max="13" width="6.83203125" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="15" width="8" customWidth="1"/>
+    <col min="16" max="16" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
+    <col min="19" max="19" width="9.5" customWidth="1"/>
+    <col min="20" max="20" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.5" customWidth="1"/>
+    <col min="27" max="28" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="48" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q1" s="21"/>
+    </row>
     <row r="2" spans="1:28" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:28" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q3" s="21"/>
+    </row>
     <row r="4" spans="1:28" ht="13.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>1</v>
@@ -4237,91 +4215,93 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:28" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:28" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q7" s="21"/>
+    </row>
     <row r="8" spans="1:28" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="L8" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="N8" s="13" t="s">
+      <c r="N8" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="O8" s="13" t="s">
+      <c r="O8" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="P8" s="13" t="s">
+      <c r="P8" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="Q8" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="R8" s="15" t="s">
+      <c r="Q8" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="R8" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="S8" s="15" t="s">
+      <c r="S8" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="T8" s="13" t="s">
+      <c r="T8" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="U8" s="13" t="s">
+      <c r="U8" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="V8" s="13" t="s">
+      <c r="V8" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="W8" s="13" t="s">
+      <c r="W8" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="X8" s="13" t="s">
+      <c r="X8" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="Y8" s="13" t="s">
+      <c r="Y8" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="Z8" s="13" t="s">
+      <c r="Z8" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="AA8" s="13" t="s">
+      <c r="AA8" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="AB8" s="13" t="s">
+      <c r="AB8" s="12" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+      <c r="A9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
@@ -4334,3983 +4314,3981 @@
       <c r="G9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16">
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15">
         <v>22.06</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="P9" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="Q9" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16" t="s">
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="W9" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="X9" s="16" t="s">
+      <c r="X9" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="Y9" s="16" t="s">
+      <c r="Y9" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16" t="s">
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="AB9" s="16" t="s">
-        <v>85</v>
+      <c r="AB9" s="15" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="17">
+      <c r="A10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="16">
         <f t="shared" ref="D10" si="0">SUM(D11:D458)</f>
         <v>10943.041000000001</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="16">
         <f t="shared" ref="E10" si="1">SUM(E11:E458)</f>
         <v>1823.9380000000001</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="16">
         <f t="shared" ref="F10" si="2">SUM(F11:F458)</f>
         <v>2297.4469999999997</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="16">
         <f t="shared" ref="G10" si="3">SUM(G11:G458)</f>
         <v>9944.6679999999997</v>
       </c>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="17">
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="16">
         <f t="shared" ref="L10:R10" si="4">SUM(L11:L458)</f>
         <v>2361.674</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="16">
         <f t="shared" si="4"/>
         <v>-64.227000000000004</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="16">
         <f t="shared" si="4"/>
         <v>908</v>
       </c>
-      <c r="P10" s="17">
+      <c r="P10" s="16">
         <f t="shared" si="4"/>
         <v>459.4894000000001</v>
       </c>
-      <c r="Q10" s="17">
+      <c r="Q10" s="24">
         <f t="shared" si="4"/>
-        <v>1745.318</v>
-      </c>
-      <c r="R10" s="17">
+        <v>1660.318</v>
+      </c>
+      <c r="R10" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="17">
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="16">
         <f>SUM(V11:V458)</f>
         <v>434.69040000000001</v>
       </c>
-      <c r="W10" s="17">
+      <c r="W10" s="16">
         <f>SUM(W11:W458)</f>
         <v>398.81840000000017</v>
       </c>
-      <c r="X10" s="17">
+      <c r="X10" s="16">
         <f>SUM(X11:X458)</f>
         <v>444.38119999999998</v>
       </c>
-      <c r="Y10" s="17">
+      <c r="Y10" s="16">
         <f>SUM(Y11:Y458)</f>
         <v>443.2724</v>
       </c>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17">
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16">
         <f>SUM(AA11:AA458)</f>
-        <v>335.55200000000002</v>
-      </c>
-      <c r="AB10" s="17">
+        <v>305.80200000000002</v>
+      </c>
+      <c r="AB10" s="16">
         <f>SUM(AB11:AB458)</f>
         <v>159.01660000000001</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
         <v>3323</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>245.053</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>31.533999999999999</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>39.036999999999999</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>236.09</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
         <v>1</v>
       </c>
-      <c r="L11" s="18">
+      <c r="L11" s="17">
         <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
         <v>45.973999999999997</v>
       </c>
-      <c r="M11" s="18">
+      <c r="M11" s="17">
         <f>F11-L11</f>
         <v>-6.9369999999999976</v>
       </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18">
+      <c r="N11" s="17"/>
+      <c r="O11" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="18">
+      <c r="P11" s="17">
         <f>F11/5</f>
         <v>7.8073999999999995</v>
       </c>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="18">
+      <c r="Q11" s="25"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17">
         <f>(G11+O11+Q11)/P11</f>
         <v>30.239260189051414</v>
       </c>
-      <c r="U11" s="18">
+      <c r="U11" s="17">
         <f>G11/P11</f>
         <v>30.239260189051414</v>
       </c>
-      <c r="V11" s="18">
+      <c r="V11" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
         <v>19.646799999999999</v>
       </c>
-      <c r="W11" s="18">
+      <c r="W11" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
         <v>12.090399999999999</v>
       </c>
-      <c r="X11" s="18">
+      <c r="X11" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
         <v>15.026400000000001</v>
       </c>
-      <c r="Y11" s="18">
+      <c r="Y11" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
         <v>5.952</v>
       </c>
-      <c r="Z11" s="18" t="str">
+      <c r="Z11" s="17" t="str">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
         <v>300кор</v>
       </c>
-      <c r="AA11" s="18">
+      <c r="AA11" s="17">
         <f>Q11*H11</f>
         <v>0</v>
       </c>
-      <c r="AB11" s="18">
+      <c r="AB11" s="17">
         <f>P11*H11</f>
         <v>7.8073999999999995</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
         <v>4931</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>165.32</v>
       </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10">
+      <c r="E12" s="9"/>
+      <c r="F12" s="9">
         <v>16.384</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>148.93600000000001</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
         <v>1</v>
       </c>
-      <c r="L12" s="18">
-        <v>0</v>
-      </c>
-      <c r="M12" s="18">
+      <c r="L12" s="17">
+        <v>0</v>
+      </c>
+      <c r="M12" s="17">
         <f t="shared" ref="M12:M57" si="5">F12-L12</f>
         <v>16.384</v>
       </c>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18">
+      <c r="N12" s="17"/>
+      <c r="O12" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
         <v>0</v>
       </c>
-      <c r="P12" s="18">
+      <c r="P12" s="17">
         <f t="shared" ref="P12:P57" si="6">F12/5</f>
         <v>3.2768000000000002</v>
       </c>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18">
+      <c r="Q12" s="25"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17">
         <f t="shared" ref="T12:T57" si="7">(G12+O12+Q12)/P12</f>
         <v>45.45166015625</v>
       </c>
-      <c r="U12" s="18">
+      <c r="U12" s="17">
         <f t="shared" ref="U12:U57" si="8">G12/P12</f>
         <v>45.45166015625</v>
       </c>
-      <c r="V12" s="18">
+      <c r="V12" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
         <v>0</v>
       </c>
-      <c r="W12" s="18">
+      <c r="W12" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
         <v>0</v>
       </c>
-      <c r="X12" s="18">
+      <c r="X12" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
         <v>1.9536000000000002</v>
       </c>
-      <c r="Y12" s="18">
+      <c r="Y12" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
         <v>4.0444000000000004</v>
       </c>
-      <c r="Z12" s="18"/>
-      <c r="AA12" s="18">
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17">
         <f t="shared" ref="AA12:AA57" si="9">Q12*H12</f>
         <v>0</v>
       </c>
-      <c r="AB12" s="18">
+      <c r="AB12" s="17">
         <f t="shared" ref="AB12:AB57" si="10">P12*H12</f>
         <v>3.2768000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
         <v>5579</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>-10</v>
       </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10">
-        <v>0</v>
-      </c>
-      <c r="G13" s="10">
+      <c r="E13" s="9"/>
+      <c r="F13" s="9">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
         <v>-10</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
         <v>0.42</v>
       </c>
-      <c r="L13" s="18">
+      <c r="L13" s="17">
         <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
         <v>23</v>
       </c>
-      <c r="M13" s="18">
+      <c r="M13" s="17">
         <f t="shared" si="5"/>
         <v>-23</v>
       </c>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18">
+      <c r="N13" s="17"/>
+      <c r="O13" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
         <v>22</v>
       </c>
-      <c r="P13" s="18">
+      <c r="P13" s="17">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T13" s="18" t="e">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T13" s="17" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U13" s="18" t="e">
+      <c r="U13" s="17" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V13" s="18">
+      <c r="V13" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
         <v>8</v>
       </c>
-      <c r="W13" s="18">
+      <c r="W13" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
         <v>5.6</v>
       </c>
-      <c r="X13" s="18">
+      <c r="X13" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
         <v>2</v>
       </c>
-      <c r="Y13" s="18">
+      <c r="Y13" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
         <v>0.6</v>
       </c>
-      <c r="Z13" s="18"/>
-      <c r="AA13" s="18">
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AB13" s="18">
+      <c r="AB13" s="17">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
         <v>5754</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>245.12200000000001</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>40.5</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <v>27.21</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>217.91200000000001</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
         <v>1</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L14" s="17">
         <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
         <v>27</v>
       </c>
-      <c r="M14" s="18">
+      <c r="M14" s="17">
         <f t="shared" si="5"/>
         <v>0.21000000000000085</v>
       </c>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18">
+      <c r="N14" s="17"/>
+      <c r="O14" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="18">
+      <c r="P14" s="17">
         <f t="shared" si="6"/>
         <v>5.4420000000000002</v>
       </c>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T14" s="18">
+      <c r="Q14" s="25"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T14" s="17">
         <f t="shared" si="7"/>
         <v>40.042631385520032</v>
       </c>
-      <c r="U14" s="18">
+      <c r="U14" s="17">
         <f t="shared" si="8"/>
         <v>40.042631385520032</v>
       </c>
-      <c r="V14" s="18">
+      <c r="V14" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
         <v>11.7</v>
       </c>
-      <c r="W14" s="18">
+      <c r="W14" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
         <v>12.6</v>
       </c>
-      <c r="X14" s="18">
+      <c r="X14" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
         <v>5.4</v>
       </c>
-      <c r="Y14" s="18">
+      <c r="Y14" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
         <v>9.9</v>
       </c>
-      <c r="Z14" s="18"/>
-      <c r="AA14" s="18">
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="18">
+      <c r="AB14" s="17">
         <f t="shared" si="10"/>
         <v>5.4420000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
         <v>5755</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>327.72</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <v>4.59</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <v>9.1579999999999995</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>318.56200000000001</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
         <v>1</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L15" s="17">
         <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
         <v>13.5</v>
       </c>
-      <c r="M15" s="18">
+      <c r="M15" s="17">
         <f t="shared" si="5"/>
         <v>-4.3420000000000005</v>
       </c>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18">
+      <c r="N15" s="17"/>
+      <c r="O15" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
         <v>0</v>
       </c>
-      <c r="P15" s="18">
+      <c r="P15" s="17">
         <f t="shared" si="6"/>
         <v>1.8315999999999999</v>
       </c>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T15" s="18">
+      <c r="Q15" s="25"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T15" s="17">
         <f t="shared" si="7"/>
         <v>173.92552959161389</v>
       </c>
-      <c r="U15" s="18">
+      <c r="U15" s="17">
         <f t="shared" si="8"/>
         <v>173.92552959161389</v>
       </c>
-      <c r="V15" s="18">
+      <c r="V15" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
         <v>7.2</v>
       </c>
-      <c r="W15" s="18">
+      <c r="W15" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
         <v>6.3</v>
       </c>
-      <c r="X15" s="18">
+      <c r="X15" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
         <v>5.4</v>
       </c>
-      <c r="Y15" s="18">
+      <c r="Y15" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
         <v>1.8</v>
       </c>
-      <c r="Z15" s="18"/>
-      <c r="AA15" s="18">
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AB15" s="18">
+      <c r="AB15" s="17">
         <f t="shared" si="10"/>
         <v>1.8315999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
         <v>5897</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="10">
+      <c r="D16" s="10"/>
+      <c r="E16" s="9">
         <v>5</v>
       </c>
-      <c r="F16" s="10">
-        <v>0</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="5">
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9"/>
+      <c r="H16">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
         <v>0.42</v>
       </c>
-      <c r="L16" s="18">
+      <c r="L16" s="17">
         <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
         <v>4</v>
       </c>
-      <c r="M16" s="18">
+      <c r="M16" s="17">
         <f t="shared" si="5"/>
         <v>-4</v>
       </c>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18">
+      <c r="N16" s="17"/>
+      <c r="O16" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
         <v>52</v>
       </c>
-      <c r="P16" s="18">
+      <c r="P16" s="17">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T16" s="18" t="e">
+      <c r="Q16" s="25"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T16" s="17" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U16" s="18" t="e">
+      <c r="U16" s="17" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V16" s="18">
+      <c r="V16" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
         <v>8.8000000000000007</v>
       </c>
-      <c r="W16" s="18">
+      <c r="W16" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
         <v>5.6</v>
       </c>
-      <c r="X16" s="18">
+      <c r="X16" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
         <v>3.8</v>
       </c>
-      <c r="Y16" s="18">
+      <c r="Y16" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
         <v>2.6</v>
       </c>
-      <c r="Z16" s="18"/>
-      <c r="AA16" s="18">
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AB16" s="18">
+      <c r="AB16" s="17">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="8">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
         <v>6148</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>343</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>65</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>46</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>297</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
         <v>0.3</v>
       </c>
-      <c r="L17" s="18">
+      <c r="L17" s="17">
         <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
         <v>52</v>
       </c>
-      <c r="M17" s="18">
+      <c r="M17" s="17">
         <f t="shared" si="5"/>
         <v>-6</v>
       </c>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18">
+      <c r="N17" s="17"/>
+      <c r="O17" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="18">
+      <c r="P17" s="17">
         <f t="shared" si="6"/>
         <v>9.1999999999999993</v>
       </c>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T17" s="18">
+      <c r="Q17" s="25"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T17" s="17">
         <f t="shared" si="7"/>
         <v>32.282608695652179</v>
       </c>
-      <c r="U17" s="18">
+      <c r="U17" s="17">
         <f t="shared" si="8"/>
         <v>32.282608695652179</v>
       </c>
-      <c r="V17" s="18">
+      <c r="V17" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
         <v>6.6</v>
       </c>
-      <c r="W17" s="18">
+      <c r="W17" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="18">
+      <c r="X17" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
         <v>8.8000000000000007</v>
       </c>
-      <c r="Y17" s="18">
+      <c r="Y17" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
         <v>11.4</v>
       </c>
-      <c r="Z17" s="18"/>
-      <c r="AA17" s="18">
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AB17" s="18">
+      <c r="AB17" s="17">
         <f t="shared" si="10"/>
         <v>2.76</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="8">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
         <v>6149</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>481</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>68</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <v>43</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>438</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
         <v>0.3</v>
       </c>
-      <c r="L18" s="18">
+      <c r="L18" s="17">
         <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
         <v>4</v>
       </c>
-      <c r="M18" s="18">
+      <c r="M18" s="17">
         <f t="shared" si="5"/>
         <v>39</v>
       </c>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18">
+      <c r="N18" s="17"/>
+      <c r="O18" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
         <v>0</v>
       </c>
-      <c r="P18" s="18">
+      <c r="P18" s="17">
         <f t="shared" si="6"/>
         <v>8.6</v>
       </c>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T18" s="18">
+      <c r="Q18" s="25"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T18" s="17">
         <f t="shared" si="7"/>
         <v>50.930232558139537</v>
       </c>
-      <c r="U18" s="18">
+      <c r="U18" s="17">
         <f t="shared" si="8"/>
         <v>50.930232558139537</v>
       </c>
-      <c r="V18" s="18">
+      <c r="V18" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
         <v>7</v>
       </c>
-      <c r="W18" s="18">
+      <c r="W18" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
         <v>0</v>
       </c>
-      <c r="X18" s="18">
+      <c r="X18" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
         <v>9.1999999999999993</v>
       </c>
-      <c r="Y18" s="18">
+      <c r="Y18" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
         <v>14.6</v>
       </c>
-      <c r="Z18" s="18"/>
-      <c r="AA18" s="18">
+      <c r="Z18" s="17"/>
+      <c r="AA18" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AB18" s="18">
+      <c r="AB18" s="17">
         <f t="shared" si="10"/>
         <v>2.5799999999999996</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="8">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
         <v>6168</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>504</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>85</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <v>118</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>387</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
         <v>0.35</v>
       </c>
-      <c r="L19" s="18">
+      <c r="L19" s="17">
         <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
         <v>128</v>
       </c>
-      <c r="M19" s="18">
+      <c r="M19" s="17">
         <f t="shared" si="5"/>
         <v>-10</v>
       </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18">
+      <c r="N19" s="17"/>
+      <c r="O19" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
         <v>0</v>
       </c>
-      <c r="P19" s="18">
+      <c r="P19" s="17">
         <f t="shared" si="6"/>
         <v>23.6</v>
       </c>
-      <c r="Q19" s="19">
-        <f t="shared" ref="Q19:Q53" si="11">20*P19-G19-O19</f>
+      <c r="Q19" s="25">
+        <v>0</v>
+      </c>
+      <c r="R19" s="18"/>
+      <c r="S19" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="R19" s="19"/>
-      <c r="S19" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T19" s="18">
+      <c r="T19" s="17">
+        <f t="shared" si="7"/>
+        <v>16.398305084745761</v>
+      </c>
+      <c r="U19" s="17">
+        <f t="shared" si="8"/>
+        <v>16.398305084745761</v>
+      </c>
+      <c r="V19" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>8</v>
+      </c>
+      <c r="W19" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>0.2</v>
+      </c>
+      <c r="X19" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>8.6</v>
+      </c>
+      <c r="Y19" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>10.4</v>
+      </c>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="17">
+        <f t="shared" si="10"/>
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>6202</v>
+      </c>
+      <c r="D20" s="9">
+        <v>324</v>
+      </c>
+      <c r="E20" s="9">
+        <v>39</v>
+      </c>
+      <c r="F20" s="9">
+        <v>54</v>
+      </c>
+      <c r="G20" s="9">
+        <v>270</v>
+      </c>
+      <c r="H20">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.3</v>
+      </c>
+      <c r="L20" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>64</v>
+      </c>
+      <c r="M20" s="17">
+        <f t="shared" si="5"/>
+        <v>-10</v>
+      </c>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="17">
+        <f t="shared" si="6"/>
+        <v>10.8</v>
+      </c>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T20" s="17">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="U20" s="17">
+        <f t="shared" si="8"/>
+        <v>25</v>
+      </c>
+      <c r="V20" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="W20" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X20" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y20" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>9.6</v>
+      </c>
+      <c r="Z20" s="17"/>
+      <c r="AA20" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB20" s="17">
+        <f t="shared" si="10"/>
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>6209</v>
+      </c>
+      <c r="D21" s="9">
+        <v>495</v>
+      </c>
+      <c r="E21" s="9">
+        <v>91</v>
+      </c>
+      <c r="F21" s="9">
+        <v>73</v>
+      </c>
+      <c r="G21" s="9">
+        <v>422</v>
+      </c>
+      <c r="H21">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.35</v>
+      </c>
+      <c r="L21" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>89</v>
+      </c>
+      <c r="M21" s="17">
+        <f t="shared" si="5"/>
+        <v>-16</v>
+      </c>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="17">
+        <f t="shared" si="6"/>
+        <v>14.6</v>
+      </c>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T21" s="17">
+        <f t="shared" si="7"/>
+        <v>28.904109589041095</v>
+      </c>
+      <c r="U21" s="17">
+        <f t="shared" si="8"/>
+        <v>28.904109589041095</v>
+      </c>
+      <c r="V21" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>6.6</v>
+      </c>
+      <c r="W21" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X21" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Y21" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>11.8</v>
+      </c>
+      <c r="Z21" s="17"/>
+      <c r="AA21" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB21" s="17">
+        <f t="shared" si="10"/>
+        <v>5.1099999999999994</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>6948249</v>
+      </c>
+      <c r="D22" s="9">
+        <v>28</v>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9">
+        <v>12</v>
+      </c>
+      <c r="G22" s="9">
+        <v>16</v>
+      </c>
+      <c r="H22">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.82450000000000001</v>
+      </c>
+      <c r="I22">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>180</v>
+      </c>
+      <c r="L22" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>12</v>
+      </c>
+      <c r="M22" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="17">
+        <f t="shared" si="6"/>
+        <v>2.4</v>
+      </c>
+      <c r="Q22" s="25">
+        <f t="shared" ref="Q19:Q53" si="11">20*P22-G22-O22</f>
+        <v>32</v>
+      </c>
+      <c r="R22" s="18"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="U19" s="18">
+      <c r="U22" s="17">
         <f t="shared" si="8"/>
-        <v>16.398305084745761</v>
-      </c>
-      <c r="V19" s="18">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="V22" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>1.4</v>
+      </c>
+      <c r="W22" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>1.2</v>
+      </c>
+      <c r="X22" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>0.6</v>
+      </c>
+      <c r="Y22" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>0.4</v>
+      </c>
+      <c r="Z22" s="17"/>
+      <c r="AA22" s="17">
+        <f t="shared" si="9"/>
+        <v>26.384</v>
+      </c>
+      <c r="AB22" s="17">
+        <f t="shared" si="10"/>
+        <v>1.9787999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>6948256</v>
+      </c>
+      <c r="D23" s="9">
+        <v>411</v>
+      </c>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9">
+        <v>77</v>
+      </c>
+      <c r="G23" s="9">
+        <v>334</v>
+      </c>
+      <c r="H23">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.372</v>
+      </c>
+      <c r="L23" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>84</v>
+      </c>
+      <c r="M23" s="17">
+        <f t="shared" si="5"/>
+        <v>-7</v>
+      </c>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="17">
+        <f t="shared" si="6"/>
+        <v>15.4</v>
+      </c>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17">
+        <f t="shared" si="7"/>
+        <v>21.688311688311689</v>
+      </c>
+      <c r="U23" s="17">
+        <f t="shared" si="8"/>
+        <v>21.688311688311689</v>
+      </c>
+      <c r="V23" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>3.4</v>
+      </c>
+      <c r="W23" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>30.8</v>
+      </c>
+      <c r="X23" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>21.8</v>
+      </c>
+      <c r="Y23" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>20.2</v>
+      </c>
+      <c r="Z23" s="17"/>
+      <c r="AA23" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="17">
+        <f t="shared" si="10"/>
+        <v>5.7287999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>6948263</v>
+      </c>
+      <c r="D24" s="9">
+        <v>428</v>
+      </c>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9">
+        <v>40</v>
+      </c>
+      <c r="G24" s="9">
+        <v>388</v>
+      </c>
+      <c r="H24">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="I24">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>180</v>
+      </c>
+      <c r="L24" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>47</v>
+      </c>
+      <c r="M24" s="17">
+        <f t="shared" si="5"/>
+        <v>-7</v>
+      </c>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="17">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="W19" s="18">
+      <c r="Q24" s="25"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17">
+        <f t="shared" si="7"/>
+        <v>48.5</v>
+      </c>
+      <c r="U24" s="17">
+        <f t="shared" si="8"/>
+        <v>48.5</v>
+      </c>
+      <c r="V24" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="W24" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>30.2</v>
+      </c>
+      <c r="X24" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>20.2</v>
+      </c>
+      <c r="Y24" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="Z24" s="17"/>
+      <c r="AA24" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="17">
+        <f t="shared" si="10"/>
+        <v>5.952</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>6948270</v>
+      </c>
+      <c r="D25" s="9">
+        <v>669</v>
+      </c>
+      <c r="E25" s="9">
+        <v>552</v>
+      </c>
+      <c r="F25" s="9">
+        <v>175</v>
+      </c>
+      <c r="G25" s="9">
+        <v>1046</v>
+      </c>
+      <c r="H25">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.372</v>
+      </c>
+      <c r="I25">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>180</v>
+      </c>
+      <c r="L25" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>199</v>
+      </c>
+      <c r="M25" s="17">
+        <f t="shared" si="5"/>
+        <v>-24</v>
+      </c>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="17">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17">
+        <f t="shared" si="7"/>
+        <v>29.885714285714286</v>
+      </c>
+      <c r="U25" s="17">
+        <f t="shared" si="8"/>
+        <v>29.885714285714286</v>
+      </c>
+      <c r="V25" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>33.6</v>
+      </c>
+      <c r="W25" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>10.4</v>
+      </c>
+      <c r="X25" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>70.400000000000006</v>
+      </c>
+      <c r="Y25" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>33.6</v>
+      </c>
+      <c r="Z25" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA25" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="17">
+        <f t="shared" si="10"/>
+        <v>13.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>6948287</v>
+      </c>
+      <c r="D26" s="9">
+        <v>551</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9">
+        <v>127</v>
+      </c>
+      <c r="G26" s="9">
+        <v>424</v>
+      </c>
+      <c r="H26">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="I26">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>180</v>
+      </c>
+      <c r="L26" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>141</v>
+      </c>
+      <c r="M26" s="17">
+        <f t="shared" si="5"/>
+        <v>-14</v>
+      </c>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>273</v>
+      </c>
+      <c r="P26" s="17">
+        <f t="shared" si="6"/>
+        <v>25.4</v>
+      </c>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17">
+        <f t="shared" si="7"/>
+        <v>27.440944881889767</v>
+      </c>
+      <c r="U26" s="17">
+        <f t="shared" si="8"/>
+        <v>16.692913385826774</v>
+      </c>
+      <c r="V26" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>41.2</v>
+      </c>
+      <c r="W26" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>40.6</v>
+      </c>
+      <c r="X26" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>14.2</v>
+      </c>
+      <c r="Y26" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>41.2</v>
+      </c>
+      <c r="Z26" s="17"/>
+      <c r="AA26" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB26" s="17">
+        <f t="shared" si="10"/>
+        <v>18.897599999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>9988438</v>
+      </c>
+      <c r="D27" s="9">
+        <v>130</v>
+      </c>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9">
+        <v>29</v>
+      </c>
+      <c r="G27" s="9">
+        <v>101</v>
+      </c>
+      <c r="H27">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="I27">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>270</v>
+      </c>
+      <c r="L27" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>30</v>
+      </c>
+      <c r="M27" s="17">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>26</v>
+      </c>
+      <c r="P27" s="17">
+        <f t="shared" si="6"/>
+        <v>5.8</v>
+      </c>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17">
+        <f t="shared" si="7"/>
+        <v>21.896551724137932</v>
+      </c>
+      <c r="U27" s="17">
+        <f t="shared" si="8"/>
+        <v>17.413793103448278</v>
+      </c>
+      <c r="V27" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W27" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>6</v>
+      </c>
+      <c r="X27" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>2.8</v>
+      </c>
+      <c r="Y27" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>7.8</v>
+      </c>
+      <c r="Z27" s="17"/>
+      <c r="AA27" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB27" s="17">
+        <f t="shared" si="10"/>
+        <v>1.044</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="9">
+        <v>35</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>35</v>
+      </c>
+      <c r="H28">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="L28" s="17">
+        <v>0</v>
+      </c>
+      <c r="M28" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17">
+        <v>0</v>
+      </c>
+      <c r="P28" s="17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U28" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V28" s="17">
+        <v>0</v>
+      </c>
+      <c r="W28" s="17">
+        <v>0</v>
+      </c>
+      <c r="X28" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="9">
+        <v>153</v>
+      </c>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9"/>
+      <c r="H29">
+        <v>0.18</v>
+      </c>
+      <c r="L29" s="17">
+        <v>0</v>
+      </c>
+      <c r="M29" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17">
+        <v>0</v>
+      </c>
+      <c r="P29" s="17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U29" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V29" s="17">
+        <v>0</v>
+      </c>
+      <c r="W29" s="17">
+        <v>0</v>
+      </c>
+      <c r="X29" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="17"/>
+      <c r="AA29" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="9">
+        <v>17</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>17</v>
+      </c>
+      <c r="H30">
+        <v>0.18</v>
+      </c>
+      <c r="L30" s="17">
+        <v>0</v>
+      </c>
+      <c r="M30" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17">
+        <v>0</v>
+      </c>
+      <c r="P30" s="17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U30" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V30" s="17">
+        <v>0</v>
+      </c>
+      <c r="W30" s="17">
+        <v>0</v>
+      </c>
+      <c r="X30" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="17"/>
+      <c r="AA30" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>1018967</v>
+      </c>
+      <c r="D31" s="9">
+        <v>68</v>
+      </c>
+      <c r="E31" s="9">
+        <v>220</v>
+      </c>
+      <c r="F31" s="9">
+        <v>75</v>
+      </c>
+      <c r="G31" s="9">
+        <v>211</v>
+      </c>
+      <c r="H31">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="I31">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>120</v>
+      </c>
+      <c r="L31" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>77</v>
+      </c>
+      <c r="M31" s="17">
+        <f t="shared" si="5"/>
+        <v>-2</v>
+      </c>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>144</v>
+      </c>
+      <c r="P31" s="17">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17">
+        <f t="shared" si="7"/>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="U31" s="17">
+        <f t="shared" si="8"/>
+        <v>14.066666666666666</v>
+      </c>
+      <c r="V31" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>6.2</v>
+      </c>
+      <c r="W31" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>13.8</v>
+      </c>
+      <c r="X31" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>20</v>
+      </c>
+      <c r="Y31" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>21.6</v>
+      </c>
+      <c r="Z31" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA31" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB31" s="17">
+        <f t="shared" si="10"/>
+        <v>2.6999999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>1018950</v>
+      </c>
+      <c r="D32" s="9">
+        <v>1583</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9">
+        <v>104</v>
+      </c>
+      <c r="G32" s="9">
+        <v>1479</v>
+      </c>
+      <c r="H32">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="I32">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>120</v>
+      </c>
+      <c r="L32" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>104</v>
+      </c>
+      <c r="M32" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P32" s="17">
+        <f t="shared" si="6"/>
+        <v>20.8</v>
+      </c>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17">
+        <f t="shared" si="7"/>
+        <v>71.105769230769226</v>
+      </c>
+      <c r="U32" s="17">
+        <f t="shared" si="8"/>
+        <v>71.105769230769226</v>
+      </c>
+      <c r="V32" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="W32" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>19</v>
+      </c>
+      <c r="X32" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>25</v>
+      </c>
+      <c r="Y32" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>25</v>
+      </c>
+      <c r="Z32" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA32" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB32" s="17">
+        <f t="shared" si="10"/>
+        <v>3.7439999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>9988476</v>
+      </c>
+      <c r="D33" s="9">
+        <v>175</v>
+      </c>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9">
+        <v>23</v>
+      </c>
+      <c r="G33" s="9">
+        <v>152</v>
+      </c>
+      <c r="H33">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.4</v>
+      </c>
+      <c r="I33">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>270</v>
+      </c>
+      <c r="L33" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>24</v>
+      </c>
+      <c r="M33" s="17">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="17">
+        <f t="shared" si="6"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17">
+        <f t="shared" si="7"/>
+        <v>33.04347826086957</v>
+      </c>
+      <c r="U33" s="17">
+        <f t="shared" si="8"/>
+        <v>33.04347826086957</v>
+      </c>
+      <c r="V33" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>10</v>
+      </c>
+      <c r="W33" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X33" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>1.8</v>
+      </c>
+      <c r="Y33" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>2.4</v>
+      </c>
+      <c r="Z33" s="17"/>
+      <c r="AA33" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB33" s="17">
+        <f t="shared" si="10"/>
+        <v>1.8399999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="9">
+        <v>-1</v>
+      </c>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>-1</v>
+      </c>
+      <c r="H34">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.4</v>
+      </c>
+      <c r="L34" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="M34" s="17">
+        <f t="shared" si="5"/>
+        <v>-3</v>
+      </c>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>5</v>
+      </c>
+      <c r="P34" s="17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U34" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V34" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W34" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X34" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
         <v>0.2</v>
       </c>
-      <c r="X19" s="18">
+      <c r="Z34" s="17"/>
+      <c r="AA34" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB34" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>5034819</v>
+      </c>
+      <c r="D35" s="9">
+        <v>-42</v>
+      </c>
+      <c r="E35" s="9">
+        <v>153</v>
+      </c>
+      <c r="F35" s="9">
+        <v>7</v>
+      </c>
+      <c r="G35" s="9">
+        <v>102</v>
+      </c>
+      <c r="H35">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="L35" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>10</v>
+      </c>
+      <c r="M35" s="17">
+        <f t="shared" si="5"/>
+        <v>-3</v>
+      </c>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P35" s="17">
+        <f t="shared" si="6"/>
+        <v>1.4</v>
+      </c>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17">
+        <f t="shared" si="7"/>
+        <v>72.857142857142861</v>
+      </c>
+      <c r="U35" s="17">
+        <f t="shared" si="8"/>
+        <v>72.857142857142861</v>
+      </c>
+      <c r="V35" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>7.4</v>
+      </c>
+      <c r="W35" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="X35" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>3.8</v>
+      </c>
+      <c r="Y35" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>3.2</v>
+      </c>
+      <c r="Z35" s="17"/>
+      <c r="AA35" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB35" s="17">
+        <f t="shared" si="10"/>
+        <v>0.252</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>8445177</v>
+      </c>
+      <c r="D36" s="9">
+        <v>115</v>
+      </c>
+      <c r="E36" s="9">
+        <v>3</v>
+      </c>
+      <c r="F36" s="9">
+        <v>44</v>
+      </c>
+      <c r="G36" s="9">
+        <v>72</v>
+      </c>
+      <c r="H36">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="L36" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>46</v>
+      </c>
+      <c r="M36" s="17">
+        <f t="shared" si="5"/>
+        <v>-2</v>
+      </c>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>61</v>
+      </c>
+      <c r="P36" s="17">
+        <f t="shared" si="6"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="Q36" s="25">
+        <f t="shared" si="11"/>
+        <v>43</v>
+      </c>
+      <c r="R36" s="18"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U36" s="17">
+        <f t="shared" si="8"/>
+        <v>8.1818181818181817</v>
+      </c>
+      <c r="V36" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="W36" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>0.4</v>
+      </c>
+      <c r="X36" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>6.2</v>
+      </c>
+      <c r="Y36" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="Z36" s="17"/>
+      <c r="AA36" s="17">
+        <f t="shared" si="9"/>
+        <v>4.3</v>
+      </c>
+      <c r="AB36" s="17">
+        <f t="shared" si="10"/>
+        <v>0.88000000000000012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>5038411</v>
+      </c>
+      <c r="D37" s="9">
+        <v>337</v>
+      </c>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9">
+        <v>119</v>
+      </c>
+      <c r="G37" s="9">
+        <v>218</v>
+      </c>
+      <c r="H37">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="I37">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>150</v>
+      </c>
+      <c r="L37" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>129</v>
+      </c>
+      <c r="M37" s="17">
+        <f t="shared" si="5"/>
+        <v>-10</v>
+      </c>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P37" s="17">
+        <f t="shared" si="6"/>
+        <v>23.8</v>
+      </c>
+      <c r="Q37" s="25">
+        <f t="shared" si="11"/>
+        <v>258</v>
+      </c>
+      <c r="R37" s="18"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U37" s="17">
+        <f t="shared" si="8"/>
+        <v>9.1596638655462179</v>
+      </c>
+      <c r="V37" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>19</v>
+      </c>
+      <c r="W37" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>27.2</v>
+      </c>
+      <c r="X37" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>27.6</v>
+      </c>
+      <c r="Y37" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>13</v>
+      </c>
+      <c r="Z37" s="17"/>
+      <c r="AA37" s="17">
+        <f t="shared" si="9"/>
+        <v>46.44</v>
+      </c>
+      <c r="AB37" s="17">
+        <f t="shared" si="10"/>
+        <v>4.2839999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="9">
+        <v>36.363999999999997</v>
+      </c>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>36.363999999999997</v>
+      </c>
+      <c r="H38">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="17">
+        <v>0</v>
+      </c>
+      <c r="M38" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P38" s="17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="25"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U38" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V38" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W38" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X38" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="17"/>
+      <c r="AA38" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB38" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>5038459</v>
+      </c>
+      <c r="D39" s="9">
+        <v>398</v>
+      </c>
+      <c r="E39" s="9">
+        <v>1</v>
+      </c>
+      <c r="F39" s="9">
+        <v>128</v>
+      </c>
+      <c r="G39" s="9">
+        <v>270</v>
+      </c>
+      <c r="H39">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="I39">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>150</v>
+      </c>
+      <c r="L39" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>140</v>
+      </c>
+      <c r="M39" s="17">
+        <f t="shared" si="5"/>
+        <v>-12</v>
+      </c>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="17">
+        <f t="shared" si="6"/>
+        <v>25.6</v>
+      </c>
+      <c r="Q39" s="25">
+        <f t="shared" si="11"/>
+        <v>242</v>
+      </c>
+      <c r="R39" s="18"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U39" s="17">
+        <f t="shared" si="8"/>
+        <v>10.546875</v>
+      </c>
+      <c r="V39" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>23.2</v>
+      </c>
+      <c r="W39" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>29.6</v>
+      </c>
+      <c r="X39" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>23.4</v>
+      </c>
+      <c r="Y39" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="Z39" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA39" s="17">
+        <f t="shared" si="9"/>
+        <v>43.559999999999995</v>
+      </c>
+      <c r="AB39" s="17">
+        <f t="shared" si="10"/>
+        <v>4.6079999999999997</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>5038831</v>
+      </c>
+      <c r="D40" s="9">
+        <v>283</v>
+      </c>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9">
+        <v>43</v>
+      </c>
+      <c r="G40" s="9">
+        <v>240</v>
+      </c>
+      <c r="H40">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="L40" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>53</v>
+      </c>
+      <c r="M40" s="17">
+        <f t="shared" si="5"/>
+        <v>-10</v>
+      </c>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P40" s="17">
+        <f t="shared" si="6"/>
         <v>8.6</v>
       </c>
-      <c r="Y19" s="18">
+      <c r="Q40" s="25"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17">
+        <f t="shared" si="7"/>
+        <v>27.906976744186046</v>
+      </c>
+      <c r="U40" s="17">
+        <f t="shared" si="8"/>
+        <v>27.906976744186046</v>
+      </c>
+      <c r="V40" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>13.2</v>
+      </c>
+      <c r="W40" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>15.2</v>
+      </c>
+      <c r="X40" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>9.6</v>
+      </c>
+      <c r="Y40" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>10.4</v>
-      </c>
-      <c r="Z19" s="18"/>
-      <c r="AA19" s="18">
+        <v>11.8</v>
+      </c>
+      <c r="Z40" s="17"/>
+      <c r="AA40" s="17">
         <f t="shared" si="9"/>
-        <v>29.749999999999996</v>
-      </c>
-      <c r="AB19" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="17">
         <f t="shared" si="10"/>
-        <v>8.26</v>
+        <v>1.5479999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="9" t="s">
+    <row r="41" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C41" s="8">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>6202</v>
-      </c>
-      <c r="D20" s="10">
-        <v>324</v>
-      </c>
-      <c r="E20" s="10">
-        <v>39</v>
-      </c>
-      <c r="F20" s="10">
+        <v>5038855</v>
+      </c>
+      <c r="D41" s="9">
+        <v>195</v>
+      </c>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9">
+        <v>36</v>
+      </c>
+      <c r="G41" s="9">
+        <v>159</v>
+      </c>
+      <c r="H41">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="L41" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>43</v>
+      </c>
+      <c r="M41" s="17">
+        <f t="shared" si="5"/>
+        <v>-7</v>
+      </c>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P41" s="17">
+        <f t="shared" si="6"/>
+        <v>7.2</v>
+      </c>
+      <c r="Q41" s="25"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17">
+        <f t="shared" si="7"/>
+        <v>22.083333333333332</v>
+      </c>
+      <c r="U41" s="17">
+        <f t="shared" si="8"/>
+        <v>22.083333333333332</v>
+      </c>
+      <c r="V41" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W41" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>6.2</v>
+      </c>
+      <c r="X41" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="Y41" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>9</v>
+      </c>
+      <c r="Z41" s="17"/>
+      <c r="AA41" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB41" s="17">
+        <f t="shared" si="10"/>
+        <v>1.296</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>5038435</v>
+      </c>
+      <c r="D42" s="9">
+        <v>262</v>
+      </c>
+      <c r="E42" s="9">
+        <v>32</v>
+      </c>
+      <c r="F42" s="9">
+        <v>137</v>
+      </c>
+      <c r="G42" s="9">
+        <v>157</v>
+      </c>
+      <c r="H42">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="I42">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>150</v>
+      </c>
+      <c r="L42" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>151</v>
+      </c>
+      <c r="M42" s="17">
+        <f t="shared" si="5"/>
+        <v>-14</v>
+      </c>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>216</v>
+      </c>
+      <c r="P42" s="17">
+        <f t="shared" si="6"/>
+        <v>27.4</v>
+      </c>
+      <c r="Q42" s="25">
+        <f t="shared" si="11"/>
+        <v>175</v>
+      </c>
+      <c r="R42" s="18"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U42" s="17">
+        <f t="shared" si="8"/>
+        <v>5.7299270072992705</v>
+      </c>
+      <c r="V42" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>32.4</v>
+      </c>
+      <c r="W42" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>24.6</v>
+      </c>
+      <c r="X42" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>20.8</v>
+      </c>
+      <c r="Y42" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>25.4</v>
+      </c>
+      <c r="Z42" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA42" s="17">
+        <f t="shared" si="9"/>
+        <v>31.5</v>
+      </c>
+      <c r="AB42" s="17">
+        <f t="shared" si="10"/>
+        <v>4.9319999999999995</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>5038398</v>
+      </c>
+      <c r="D43" s="9">
+        <v>371</v>
+      </c>
+      <c r="E43" s="9">
+        <v>150</v>
+      </c>
+      <c r="F43" s="9">
+        <v>58</v>
+      </c>
+      <c r="G43" s="9">
+        <v>463</v>
+      </c>
+      <c r="H43">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="I43">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
+        <v>120</v>
+      </c>
+      <c r="L43" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>66</v>
+      </c>
+      <c r="M43" s="17">
+        <f t="shared" si="5"/>
+        <v>-8</v>
+      </c>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P43" s="17">
+        <f t="shared" si="6"/>
+        <v>11.6</v>
+      </c>
+      <c r="Q43" s="25"/>
+      <c r="R43" s="18"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17">
+        <f t="shared" si="7"/>
+        <v>39.913793103448278</v>
+      </c>
+      <c r="U43" s="17">
+        <f t="shared" si="8"/>
+        <v>39.913793103448278</v>
+      </c>
+      <c r="V43" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="W43" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>12.8</v>
+      </c>
+      <c r="X43" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>13.2</v>
+      </c>
+      <c r="Y43" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>9.4</v>
+      </c>
+      <c r="Z43" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA43" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB43" s="17">
+        <f t="shared" si="10"/>
+        <v>2.0880000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>9988681</v>
+      </c>
+      <c r="D44" s="9">
+        <v>186</v>
+      </c>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9">
+        <v>41</v>
+      </c>
+      <c r="G44" s="9">
+        <v>145</v>
+      </c>
+      <c r="H44">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="L44" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>42</v>
+      </c>
+      <c r="M44" s="17">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P44" s="17">
+        <f t="shared" si="6"/>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="Q44" s="25">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="R44" s="18"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U44" s="17">
+        <f t="shared" si="8"/>
+        <v>17.682926829268293</v>
+      </c>
+      <c r="V44" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>12.4</v>
+      </c>
+      <c r="W44" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>5.8</v>
+      </c>
+      <c r="X44" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>7.4</v>
+      </c>
+      <c r="Y44" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>8.6</v>
+      </c>
+      <c r="Z44" s="17"/>
+      <c r="AA44" s="17">
+        <f t="shared" si="9"/>
+        <v>3.42</v>
+      </c>
+      <c r="AB44" s="17">
+        <f t="shared" si="10"/>
+        <v>1.4759999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="8" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>дубль</v>
+      </c>
+      <c r="D45" s="9">
+        <v>59.167999999999999</v>
+      </c>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9">
+        <v>6.6180000000000003</v>
+      </c>
+      <c r="G45" s="9">
+        <v>52.55</v>
+      </c>
+      <c r="H45">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L45" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="M45" s="17">
+        <f t="shared" si="5"/>
+        <v>1.6180000000000003</v>
+      </c>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P45" s="17">
+        <f t="shared" si="6"/>
+        <v>1.3236000000000001</v>
+      </c>
+      <c r="Q45" s="25"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17">
+        <f t="shared" si="7"/>
+        <v>39.702326987005129</v>
+      </c>
+      <c r="U45" s="17">
+        <f t="shared" si="8"/>
+        <v>39.702326987005129</v>
+      </c>
+      <c r="V45" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>1.3355999999999999</v>
+      </c>
+      <c r="W45" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>1.988</v>
+      </c>
+      <c r="X45" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>2.0207999999999999</v>
+      </c>
+      <c r="Y45" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>0.68840000000000001</v>
+      </c>
+      <c r="Z45" s="17"/>
+      <c r="AA45" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB45" s="17">
+        <f t="shared" si="10"/>
+        <v>1.3236000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>8785198</v>
+      </c>
+      <c r="D46" s="9">
+        <v>80.581999999999994</v>
+      </c>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9">
+        <v>18.98</v>
+      </c>
+      <c r="G46" s="9">
+        <v>61.601999999999997</v>
+      </c>
+      <c r="H46">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L46" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>20.2</v>
+      </c>
+      <c r="M46" s="17">
+        <f t="shared" si="5"/>
+        <v>-1.2199999999999989</v>
+      </c>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P46" s="17">
+        <f t="shared" si="6"/>
+        <v>3.7960000000000003</v>
+      </c>
+      <c r="Q46" s="25">
+        <f t="shared" si="11"/>
+        <v>14.318000000000005</v>
+      </c>
+      <c r="R46" s="18"/>
+      <c r="S46" s="17"/>
+      <c r="T46" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U46" s="17">
+        <f t="shared" si="8"/>
+        <v>16.228134878819809</v>
+      </c>
+      <c r="V46" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>3.8764000000000003</v>
+      </c>
+      <c r="W46" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>3.9607999999999999</v>
+      </c>
+      <c r="X46" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="Y46" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z46" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA46" s="17">
+        <f t="shared" si="9"/>
+        <v>14.318000000000005</v>
+      </c>
+      <c r="AB46" s="17">
+        <f t="shared" si="10"/>
+        <v>3.7960000000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>8444187</v>
+      </c>
+      <c r="D47" s="9">
+        <v>112</v>
+      </c>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9">
+        <v>68</v>
+      </c>
+      <c r="G47" s="9">
+        <v>42</v>
+      </c>
+      <c r="H47">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="L47" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>70</v>
+      </c>
+      <c r="M47" s="17">
+        <f t="shared" si="5"/>
+        <v>-2</v>
+      </c>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>52</v>
+      </c>
+      <c r="P47" s="17">
+        <f t="shared" si="6"/>
+        <v>13.6</v>
+      </c>
+      <c r="Q47" s="25">
+        <f t="shared" si="11"/>
+        <v>178</v>
+      </c>
+      <c r="R47" s="18"/>
+      <c r="S47" s="17"/>
+      <c r="T47" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U47" s="17">
+        <f t="shared" si="8"/>
+        <v>3.0882352941176472</v>
+      </c>
+      <c r="V47" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>8.6</v>
+      </c>
+      <c r="W47" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>-0.4</v>
+      </c>
+      <c r="X47" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="Y47" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="Z47" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA47" s="17">
+        <f t="shared" si="9"/>
+        <v>17.8</v>
+      </c>
+      <c r="AB47" s="17">
+        <f t="shared" si="10"/>
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>8444194</v>
+      </c>
+      <c r="D48" s="9">
+        <v>174</v>
+      </c>
+      <c r="E48" s="9">
+        <v>2</v>
+      </c>
+      <c r="F48" s="9">
+        <v>71</v>
+      </c>
+      <c r="G48" s="9">
+        <v>101</v>
+      </c>
+      <c r="H48">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="L48" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>75</v>
+      </c>
+      <c r="M48" s="17">
+        <f t="shared" si="5"/>
+        <v>-4</v>
+      </c>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P48" s="17">
+        <f t="shared" si="6"/>
+        <v>14.2</v>
+      </c>
+      <c r="Q48" s="25">
+        <f t="shared" si="11"/>
+        <v>183</v>
+      </c>
+      <c r="R48" s="18"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U48" s="17">
+        <f t="shared" si="8"/>
+        <v>7.1126760563380289</v>
+      </c>
+      <c r="V48" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>12.6</v>
+      </c>
+      <c r="W48" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>2.6</v>
+      </c>
+      <c r="X48" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>7.4</v>
+      </c>
+      <c r="Y48" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>7.6</v>
+      </c>
+      <c r="Z48" s="17"/>
+      <c r="AA48" s="17">
+        <f t="shared" si="9"/>
+        <v>18.3</v>
+      </c>
+      <c r="AB48" s="17">
+        <f t="shared" si="10"/>
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>9988391</v>
+      </c>
+      <c r="D49" s="9">
+        <v>48</v>
+      </c>
+      <c r="E49" s="9">
+        <v>64</v>
+      </c>
+      <c r="F49" s="9">
+        <v>31</v>
+      </c>
+      <c r="G49" s="9">
+        <v>81</v>
+      </c>
+      <c r="H49">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L49" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>31</v>
+      </c>
+      <c r="M49" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>32</v>
+      </c>
+      <c r="P49" s="17">
+        <f t="shared" si="6"/>
+        <v>6.2</v>
+      </c>
+      <c r="Q49" s="25">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+      <c r="R49" s="18"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U49" s="17">
+        <f t="shared" si="8"/>
+        <v>13.064516129032258</v>
+      </c>
+      <c r="V49" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W49" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>3.6</v>
+      </c>
+      <c r="X49" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>7</v>
+      </c>
+      <c r="Y49" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>7</v>
+      </c>
+      <c r="Z49" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA49" s="17">
+        <f t="shared" si="9"/>
+        <v>1.54</v>
+      </c>
+      <c r="AB49" s="17">
+        <f t="shared" si="10"/>
+        <v>0.8680000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="10">
-        <v>270</v>
-      </c>
-      <c r="H20" s="5">
+      <c r="B50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>9988377</v>
+      </c>
+      <c r="D50" s="9">
+        <v>97</v>
+      </c>
+      <c r="E50" s="9">
+        <v>32</v>
+      </c>
+      <c r="F50" s="9">
+        <v>40</v>
+      </c>
+      <c r="G50" s="9">
+        <v>89</v>
+      </c>
+      <c r="H50">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L50" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>40</v>
+      </c>
+      <c r="M50" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>25</v>
+      </c>
+      <c r="P50" s="17">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="Q50" s="25">
+        <f t="shared" si="11"/>
+        <v>46</v>
+      </c>
+      <c r="R50" s="18"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U50" s="17">
+        <f t="shared" si="8"/>
+        <v>11.125</v>
+      </c>
+      <c r="V50" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>5.2</v>
+      </c>
+      <c r="W50" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>7.4</v>
+      </c>
+      <c r="X50" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>7.4</v>
+      </c>
+      <c r="Y50" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>7.6</v>
+      </c>
+      <c r="Z50" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA50" s="17">
+        <f t="shared" si="9"/>
+        <v>6.44</v>
+      </c>
+      <c r="AB50" s="17">
+        <f t="shared" si="10"/>
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="8" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>783К798</v>
+      </c>
+      <c r="D51" s="9">
+        <v>333</v>
+      </c>
+      <c r="E51" s="9">
+        <v>72</v>
+      </c>
+      <c r="F51" s="9">
+        <v>123</v>
+      </c>
+      <c r="G51" s="9">
+        <v>210</v>
+      </c>
+      <c r="H51">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.2</v>
+      </c>
+      <c r="L51" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>123</v>
+      </c>
+      <c r="M51" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P51" s="17">
+        <f t="shared" si="6"/>
+        <v>24.6</v>
+      </c>
+      <c r="Q51" s="25">
+        <f t="shared" si="11"/>
+        <v>282</v>
+      </c>
+      <c r="R51" s="18"/>
+      <c r="S51" s="17"/>
+      <c r="T51" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U51" s="17">
+        <f t="shared" si="8"/>
+        <v>8.5365853658536572</v>
+      </c>
+      <c r="V51" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>31.8</v>
+      </c>
+      <c r="W51" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>13.8</v>
+      </c>
+      <c r="X51" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="Y51" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>13.2</v>
+      </c>
+      <c r="Z51" s="17"/>
+      <c r="AA51" s="17">
+        <f t="shared" si="9"/>
+        <v>56.400000000000006</v>
+      </c>
+      <c r="AB51" s="17">
+        <f t="shared" si="10"/>
+        <v>4.9200000000000008</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="8" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>дубль798</v>
+      </c>
+      <c r="D52" s="9">
+        <v>154.012</v>
+      </c>
+      <c r="E52" s="9">
+        <v>3.3140000000000001</v>
+      </c>
+      <c r="F52" s="9">
+        <v>15.311999999999999</v>
+      </c>
+      <c r="G52" s="9">
+        <v>138.69999999999999</v>
+      </c>
+      <c r="H52">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L52" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>25</v>
+      </c>
+      <c r="M52" s="17">
+        <f t="shared" si="5"/>
+        <v>-9.6880000000000006</v>
+      </c>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P52" s="17">
+        <f t="shared" si="6"/>
+        <v>3.0623999999999998</v>
+      </c>
+      <c r="Q52" s="25"/>
+      <c r="R52" s="18"/>
+      <c r="S52" s="17"/>
+      <c r="T52" s="17">
+        <f t="shared" si="7"/>
+        <v>45.291274817136888</v>
+      </c>
+      <c r="U52" s="17">
+        <f t="shared" si="8"/>
+        <v>45.291274817136888</v>
+      </c>
+      <c r="V52" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>3.8747999999999996</v>
+      </c>
+      <c r="W52" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>1.1103999999999998</v>
+      </c>
+      <c r="X52" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>7.4767999999999999</v>
+      </c>
+      <c r="Y52" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>3.6636000000000002</v>
+      </c>
+      <c r="Z52" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA52" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB52" s="17">
+        <f t="shared" si="10"/>
+        <v>3.0623999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="8" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>783К801</v>
+      </c>
+      <c r="D53" s="9">
+        <v>158</v>
+      </c>
+      <c r="E53" s="9">
+        <v>58</v>
+      </c>
+      <c r="F53" s="9">
+        <v>75</v>
+      </c>
+      <c r="G53" s="9">
+        <v>123</v>
+      </c>
+      <c r="H53">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.2</v>
+      </c>
+      <c r="L53" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>75</v>
+      </c>
+      <c r="M53" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P53" s="17">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="Q53" s="25">
+        <f t="shared" si="11"/>
+        <v>177</v>
+      </c>
+      <c r="R53" s="18"/>
+      <c r="S53" s="17"/>
+      <c r="T53" s="17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="U53" s="17">
+        <f t="shared" si="8"/>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="V53" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="W53" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>14</v>
+      </c>
+      <c r="X53" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>12.2</v>
+      </c>
+      <c r="Y53" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>8.6</v>
+      </c>
+      <c r="Z53" s="17"/>
+      <c r="AA53" s="17">
+        <f t="shared" si="9"/>
+        <v>35.4</v>
+      </c>
+      <c r="AB53" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="9">
+        <v>270.7</v>
+      </c>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9">
+        <v>14.747999999999999</v>
+      </c>
+      <c r="G54" s="9">
+        <v>255.952</v>
+      </c>
+      <c r="H54">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L54" s="17">
+        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
+        <v>14</v>
+      </c>
+      <c r="M54" s="17">
+        <f t="shared" si="5"/>
+        <v>0.74799999999999933</v>
+      </c>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P54" s="17">
+        <f t="shared" si="6"/>
+        <v>2.9495999999999998</v>
+      </c>
+      <c r="Q54" s="25"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="17"/>
+      <c r="T54" s="17">
+        <f t="shared" si="7"/>
+        <v>86.775155953349611</v>
+      </c>
+      <c r="U54" s="17">
+        <f t="shared" si="8"/>
+        <v>86.775155953349611</v>
+      </c>
+      <c r="V54" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>1.4567999999999999</v>
+      </c>
+      <c r="W54" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>8.5687999999999995</v>
+      </c>
+      <c r="X54" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>2.1876000000000002</v>
+      </c>
+      <c r="Y54" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>2.4E-2</v>
+      </c>
+      <c r="Z54" s="17" t="str">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
+        <v>увел продажи</v>
+      </c>
+      <c r="AA54" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB54" s="17">
+        <f t="shared" si="10"/>
+        <v>2.9495999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>3534796</v>
+      </c>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9">
+        <v>0</v>
+      </c>
+      <c r="G55" s="9"/>
+      <c r="H55">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="L55" s="17">
+        <v>0</v>
+      </c>
+      <c r="M55" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P55" s="17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q55" s="25"/>
+      <c r="R55" s="18"/>
+      <c r="S55" s="17"/>
+      <c r="T55" s="17" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U55" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V55" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W55" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X55" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y55" s="17">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z55" s="17"/>
+      <c r="AA55" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB55" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="8">
+        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
+        <v>6819</v>
+      </c>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9">
+        <v>0</v>
+      </c>
+      <c r="G56" s="9"/>
+      <c r="H56">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
         <v>0.3</v>
       </c>
-      <c r="L20" s="18">
+      <c r="L56" s="17">
         <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>64</v>
-      </c>
-      <c r="M20" s="18">
+        <v>28</v>
+      </c>
+      <c r="M56" s="17">
         <f t="shared" si="5"/>
-        <v>-10</v>
-      </c>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18">
+        <v>-28</v>
+      </c>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
         <v>0</v>
       </c>
-      <c r="P20" s="18">
+      <c r="P56" s="17">
         <f t="shared" si="6"/>
-        <v>10.8</v>
-      </c>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T20" s="18">
-        <f t="shared" si="7"/>
-        <v>25</v>
-      </c>
-      <c r="U20" s="18">
-        <f t="shared" si="8"/>
-        <v>25</v>
-      </c>
-      <c r="V20" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>4.8</v>
-      </c>
-      <c r="W20" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>1</v>
-      </c>
-      <c r="X20" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>5</v>
-      </c>
-      <c r="Y20" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>9.6</v>
-      </c>
-      <c r="Z20" s="18"/>
-      <c r="AA20" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB20" s="18">
-        <f t="shared" si="10"/>
-        <v>3.24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>6209</v>
-      </c>
-      <c r="D21" s="10">
-        <v>495</v>
-      </c>
-      <c r="E21" s="10">
-        <v>91</v>
-      </c>
-      <c r="F21" s="10">
-        <v>73</v>
-      </c>
-      <c r="G21" s="10">
-        <v>422</v>
-      </c>
-      <c r="H21" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.35</v>
-      </c>
-      <c r="L21" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>89</v>
-      </c>
-      <c r="M21" s="18">
-        <f t="shared" si="5"/>
-        <v>-16</v>
-      </c>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P21" s="18">
-        <f t="shared" si="6"/>
-        <v>14.6</v>
-      </c>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T21" s="18">
-        <f t="shared" si="7"/>
-        <v>28.904109589041095</v>
-      </c>
-      <c r="U21" s="18">
-        <f t="shared" si="8"/>
-        <v>28.904109589041095</v>
-      </c>
-      <c r="V21" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>6.6</v>
-      </c>
-      <c r="W21" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X21" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="Y21" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>11.8</v>
-      </c>
-      <c r="Z21" s="18"/>
-      <c r="AA21" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB21" s="18">
-        <f t="shared" si="10"/>
-        <v>5.1099999999999994</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>6948249</v>
-      </c>
-      <c r="D22" s="10">
-        <v>28</v>
-      </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10">
-        <v>12</v>
-      </c>
-      <c r="G22" s="10">
-        <v>16</v>
-      </c>
-      <c r="H22" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.82450000000000001</v>
-      </c>
-      <c r="I22" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>180</v>
-      </c>
-      <c r="L22" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>12</v>
-      </c>
-      <c r="M22" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P22" s="18">
-        <f t="shared" si="6"/>
-        <v>2.4</v>
-      </c>
-      <c r="Q22" s="19">
-        <f t="shared" si="11"/>
-        <v>32</v>
-      </c>
-      <c r="R22" s="19"/>
-      <c r="S22" s="18"/>
-      <c r="T22" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U22" s="18">
-        <f t="shared" si="8"/>
-        <v>6.666666666666667</v>
-      </c>
-      <c r="V22" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>1.4</v>
-      </c>
-      <c r="W22" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>1.2</v>
-      </c>
-      <c r="X22" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>0.6</v>
-      </c>
-      <c r="Y22" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>0.4</v>
-      </c>
-      <c r="Z22" s="18"/>
-      <c r="AA22" s="18">
-        <f t="shared" si="9"/>
-        <v>26.384</v>
-      </c>
-      <c r="AB22" s="18">
-        <f t="shared" si="10"/>
-        <v>1.9787999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>6948256</v>
-      </c>
-      <c r="D23" s="10">
-        <v>411</v>
-      </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10">
-        <v>77</v>
-      </c>
-      <c r="G23" s="10">
-        <v>334</v>
-      </c>
-      <c r="H23" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.372</v>
-      </c>
-      <c r="L23" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>84</v>
-      </c>
-      <c r="M23" s="18">
-        <f t="shared" si="5"/>
-        <v>-7</v>
-      </c>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P23" s="18">
-        <f t="shared" si="6"/>
-        <v>15.4</v>
-      </c>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="18"/>
-      <c r="T23" s="18">
-        <f t="shared" si="7"/>
-        <v>21.688311688311689</v>
-      </c>
-      <c r="U23" s="18">
-        <f t="shared" si="8"/>
-        <v>21.688311688311689</v>
-      </c>
-      <c r="V23" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>3.4</v>
-      </c>
-      <c r="W23" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>30.8</v>
-      </c>
-      <c r="X23" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>21.8</v>
-      </c>
-      <c r="Y23" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>20.2</v>
-      </c>
-      <c r="Z23" s="18"/>
-      <c r="AA23" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB23" s="18">
-        <f t="shared" si="10"/>
-        <v>5.7287999999999997</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>6948263</v>
-      </c>
-      <c r="D24" s="10">
-        <v>428</v>
-      </c>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10">
-        <v>40</v>
-      </c>
-      <c r="G24" s="10">
-        <v>388</v>
-      </c>
-      <c r="H24" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.74399999999999999</v>
-      </c>
-      <c r="I24" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>180</v>
-      </c>
-      <c r="L24" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>47</v>
-      </c>
-      <c r="M24" s="18">
-        <f t="shared" si="5"/>
-        <v>-7</v>
-      </c>
-      <c r="N24" s="18"/>
-      <c r="O24" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P24" s="18">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="18"/>
-      <c r="T24" s="18">
-        <f t="shared" si="7"/>
-        <v>48.5</v>
-      </c>
-      <c r="U24" s="18">
-        <f t="shared" si="8"/>
-        <v>48.5</v>
-      </c>
-      <c r="V24" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>17.399999999999999</v>
-      </c>
-      <c r="W24" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>30.2</v>
-      </c>
-      <c r="X24" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>20.2</v>
-      </c>
-      <c r="Y24" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>19.399999999999999</v>
-      </c>
-      <c r="Z24" s="18"/>
-      <c r="AA24" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB24" s="18">
-        <f t="shared" si="10"/>
-        <v>5.952</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>6948270</v>
-      </c>
-      <c r="D25" s="10">
-        <v>669</v>
-      </c>
-      <c r="E25" s="10">
-        <v>552</v>
-      </c>
-      <c r="F25" s="10">
-        <v>175</v>
-      </c>
-      <c r="G25" s="10">
-        <v>1046</v>
-      </c>
-      <c r="H25" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.372</v>
-      </c>
-      <c r="I25" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>180</v>
-      </c>
-      <c r="L25" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>199</v>
-      </c>
-      <c r="M25" s="18">
-        <f t="shared" si="5"/>
-        <v>-24</v>
-      </c>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P25" s="18">
-        <f t="shared" si="6"/>
-        <v>35</v>
-      </c>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="18"/>
-      <c r="T25" s="18">
-        <f t="shared" si="7"/>
-        <v>29.885714285714286</v>
-      </c>
-      <c r="U25" s="18">
-        <f t="shared" si="8"/>
-        <v>29.885714285714286</v>
-      </c>
-      <c r="V25" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>33.6</v>
-      </c>
-      <c r="W25" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>10.4</v>
-      </c>
-      <c r="X25" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>70.400000000000006</v>
-      </c>
-      <c r="Y25" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>33.6</v>
-      </c>
-      <c r="Z25" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA25" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB25" s="18">
-        <f t="shared" si="10"/>
-        <v>13.02</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>6948287</v>
-      </c>
-      <c r="D26" s="10">
-        <v>551</v>
-      </c>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10">
-        <v>127</v>
-      </c>
-      <c r="G26" s="10">
-        <v>424</v>
-      </c>
-      <c r="H26" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.74399999999999999</v>
-      </c>
-      <c r="I26" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>180</v>
-      </c>
-      <c r="L26" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>141</v>
-      </c>
-      <c r="M26" s="18">
-        <f t="shared" si="5"/>
-        <v>-14</v>
-      </c>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>273</v>
-      </c>
-      <c r="P26" s="18">
-        <f t="shared" si="6"/>
-        <v>25.4</v>
-      </c>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18">
-        <f t="shared" si="7"/>
-        <v>27.440944881889767</v>
-      </c>
-      <c r="U26" s="18">
-        <f t="shared" si="8"/>
-        <v>16.692913385826774</v>
-      </c>
-      <c r="V26" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>41.2</v>
-      </c>
-      <c r="W26" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>40.6</v>
-      </c>
-      <c r="X26" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>14.2</v>
-      </c>
-      <c r="Y26" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>41.2</v>
-      </c>
-      <c r="Z26" s="18"/>
-      <c r="AA26" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB26" s="18">
-        <f t="shared" si="10"/>
-        <v>18.897599999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>9988438</v>
-      </c>
-      <c r="D27" s="10">
-        <v>130</v>
-      </c>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10">
-        <v>29</v>
-      </c>
-      <c r="G27" s="10">
-        <v>101</v>
-      </c>
-      <c r="H27" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="I27" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>270</v>
-      </c>
-      <c r="L27" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>30</v>
-      </c>
-      <c r="M27" s="18">
-        <f t="shared" si="5"/>
-        <v>-1</v>
-      </c>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>26</v>
-      </c>
-      <c r="P27" s="18">
-        <f t="shared" si="6"/>
-        <v>5.8</v>
-      </c>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="18"/>
-      <c r="T27" s="18">
-        <f t="shared" si="7"/>
-        <v>21.896551724137932</v>
-      </c>
-      <c r="U27" s="18">
-        <f t="shared" si="8"/>
-        <v>17.413793103448278</v>
-      </c>
-      <c r="V27" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="W27" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>6</v>
-      </c>
-      <c r="X27" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>2.8</v>
-      </c>
-      <c r="Y27" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>7.8</v>
-      </c>
-      <c r="Z27" s="18"/>
-      <c r="AA27" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB27" s="18">
-        <f t="shared" si="10"/>
-        <v>1.044</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="10">
-        <v>35</v>
-      </c>
-      <c r="F28" s="10">
-        <v>0</v>
-      </c>
-      <c r="G28" s="10">
-        <v>35</v>
-      </c>
-      <c r="H28" s="5">
-        <v>0.82399999999999995</v>
-      </c>
-      <c r="L28" s="18">
-        <v>0</v>
-      </c>
-      <c r="M28" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="18"/>
-      <c r="O28" s="18">
-        <v>0</v>
-      </c>
-      <c r="P28" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="18"/>
-      <c r="T28" s="18" t="e">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="25"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T56" s="17" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U28" s="18" t="e">
+      <c r="U56" s="17" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V28" s="18">
-        <v>0</v>
-      </c>
-      <c r="W28" s="18">
-        <v>0</v>
-      </c>
-      <c r="X28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="18"/>
-      <c r="AA28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="10">
-        <v>153</v>
-      </c>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10">
-        <v>0</v>
-      </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="L29" s="18">
-        <v>0</v>
-      </c>
-      <c r="M29" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18">
-        <v>0</v>
-      </c>
-      <c r="P29" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U29" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V29" s="18">
-        <v>0</v>
-      </c>
-      <c r="W29" s="18">
-        <v>0</v>
-      </c>
-      <c r="X29" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="18"/>
-      <c r="AA29" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="10">
-        <v>17</v>
-      </c>
-      <c r="F30" s="10">
-        <v>0</v>
-      </c>
-      <c r="G30" s="10">
-        <v>17</v>
-      </c>
-      <c r="H30" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="L30" s="18">
-        <v>0</v>
-      </c>
-      <c r="M30" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18">
-        <v>0</v>
-      </c>
-      <c r="P30" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U30" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V30" s="18">
-        <v>0</v>
-      </c>
-      <c r="W30" s="18">
-        <v>0</v>
-      </c>
-      <c r="X30" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="18"/>
-      <c r="AA30" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>1018967</v>
-      </c>
-      <c r="D31" s="10">
-        <v>68</v>
-      </c>
-      <c r="E31" s="10">
-        <v>220</v>
-      </c>
-      <c r="F31" s="10">
-        <v>75</v>
-      </c>
-      <c r="G31" s="10">
-        <v>211</v>
-      </c>
-      <c r="H31" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="I31" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>120</v>
-      </c>
-      <c r="L31" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>77</v>
-      </c>
-      <c r="M31" s="18">
-        <f t="shared" si="5"/>
-        <v>-2</v>
-      </c>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>144</v>
-      </c>
-      <c r="P31" s="18">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18">
-        <f t="shared" si="7"/>
-        <v>23.666666666666668</v>
-      </c>
-      <c r="U31" s="18">
-        <f t="shared" si="8"/>
-        <v>14.066666666666666</v>
-      </c>
-      <c r="V31" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>6.2</v>
-      </c>
-      <c r="W31" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>13.8</v>
-      </c>
-      <c r="X31" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>20</v>
-      </c>
-      <c r="Y31" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>21.6</v>
-      </c>
-      <c r="Z31" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA31" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB31" s="18">
-        <f t="shared" si="10"/>
-        <v>2.6999999999999997</v>
-      </c>
-    </row>
-    <row r="32" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>1018950</v>
-      </c>
-      <c r="D32" s="10">
-        <v>1583</v>
-      </c>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10">
-        <v>104</v>
-      </c>
-      <c r="G32" s="10">
-        <v>1479</v>
-      </c>
-      <c r="H32" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="I32" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>120</v>
-      </c>
-      <c r="L32" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>104</v>
-      </c>
-      <c r="M32" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P32" s="18">
-        <f t="shared" si="6"/>
-        <v>20.8</v>
-      </c>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18">
-        <f t="shared" si="7"/>
-        <v>71.105769230769226</v>
-      </c>
-      <c r="U32" s="18">
-        <f t="shared" si="8"/>
-        <v>71.105769230769226</v>
-      </c>
-      <c r="V32" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>4.8</v>
-      </c>
-      <c r="W32" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>19</v>
-      </c>
-      <c r="X32" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>25</v>
-      </c>
-      <c r="Y32" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>25</v>
-      </c>
-      <c r="Z32" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA32" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB32" s="18">
-        <f t="shared" si="10"/>
-        <v>3.7439999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>9988476</v>
-      </c>
-      <c r="D33" s="10">
-        <v>175</v>
-      </c>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10">
-        <v>23</v>
-      </c>
-      <c r="G33" s="10">
-        <v>152</v>
-      </c>
-      <c r="H33" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.4</v>
-      </c>
-      <c r="I33" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>270</v>
-      </c>
-      <c r="L33" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>24</v>
-      </c>
-      <c r="M33" s="18">
-        <f t="shared" si="5"/>
-        <v>-1</v>
-      </c>
-      <c r="N33" s="18"/>
-      <c r="O33" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P33" s="18">
-        <f t="shared" si="6"/>
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="18"/>
-      <c r="T33" s="18">
-        <f t="shared" si="7"/>
-        <v>33.04347826086957</v>
-      </c>
-      <c r="U33" s="18">
-        <f t="shared" si="8"/>
-        <v>33.04347826086957</v>
-      </c>
-      <c r="V33" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>10</v>
-      </c>
-      <c r="W33" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X33" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>1.8</v>
-      </c>
-      <c r="Y33" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>2.4</v>
-      </c>
-      <c r="Z33" s="18"/>
-      <c r="AA33" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB33" s="18">
-        <f t="shared" si="10"/>
-        <v>1.8399999999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="10">
-        <v>-1</v>
-      </c>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10">
-        <v>0</v>
-      </c>
-      <c r="G34" s="10">
-        <v>-1</v>
-      </c>
-      <c r="H34" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.4</v>
-      </c>
-      <c r="L34" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="M34" s="18">
-        <f t="shared" si="5"/>
-        <v>-3</v>
-      </c>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>5</v>
-      </c>
-      <c r="P34" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U34" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V34" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W34" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X34" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>0.2</v>
-      </c>
-      <c r="Z34" s="18"/>
-      <c r="AA34" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB34" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>5034819</v>
-      </c>
-      <c r="D35" s="10">
-        <v>-42</v>
-      </c>
-      <c r="E35" s="10">
-        <v>153</v>
-      </c>
-      <c r="F35" s="10">
-        <v>7</v>
-      </c>
-      <c r="G35" s="10">
-        <v>102</v>
-      </c>
-      <c r="H35" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="L35" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>10</v>
-      </c>
-      <c r="M35" s="18">
-        <f t="shared" si="5"/>
-        <v>-3</v>
-      </c>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P35" s="18">
-        <f t="shared" si="6"/>
-        <v>1.4</v>
-      </c>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="19"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="18">
-        <f t="shared" si="7"/>
-        <v>72.857142857142861</v>
-      </c>
-      <c r="U35" s="18">
-        <f t="shared" si="8"/>
-        <v>72.857142857142861</v>
-      </c>
-      <c r="V35" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>7.4</v>
-      </c>
-      <c r="W35" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>4.8</v>
-      </c>
-      <c r="X35" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>3.8</v>
-      </c>
-      <c r="Y35" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>3.2</v>
-      </c>
-      <c r="Z35" s="18"/>
-      <c r="AA35" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB35" s="18">
-        <f t="shared" si="10"/>
-        <v>0.252</v>
-      </c>
-    </row>
-    <row r="36" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>8445177</v>
-      </c>
-      <c r="D36" s="10">
-        <v>115</v>
-      </c>
-      <c r="E36" s="10">
-        <v>3</v>
-      </c>
-      <c r="F36" s="10">
-        <v>44</v>
-      </c>
-      <c r="G36" s="10">
-        <v>72</v>
-      </c>
-      <c r="H36" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="L36" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>46</v>
-      </c>
-      <c r="M36" s="18">
-        <f t="shared" si="5"/>
-        <v>-2</v>
-      </c>
-      <c r="N36" s="18"/>
-      <c r="O36" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>61</v>
-      </c>
-      <c r="P36" s="18">
-        <f t="shared" si="6"/>
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="Q36" s="19">
-        <f t="shared" si="11"/>
-        <v>43</v>
-      </c>
-      <c r="R36" s="19"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U36" s="18">
-        <f t="shared" si="8"/>
-        <v>8.1818181818181817</v>
-      </c>
-      <c r="V36" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="W36" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>0.4</v>
-      </c>
-      <c r="X36" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>6.2</v>
-      </c>
-      <c r="Y36" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="Z36" s="18"/>
-      <c r="AA36" s="18">
-        <f t="shared" si="9"/>
-        <v>4.3</v>
-      </c>
-      <c r="AB36" s="18">
-        <f t="shared" si="10"/>
-        <v>0.88000000000000012</v>
-      </c>
-    </row>
-    <row r="37" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>5038411</v>
-      </c>
-      <c r="D37" s="10">
-        <v>337</v>
-      </c>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10">
-        <v>119</v>
-      </c>
-      <c r="G37" s="10">
-        <v>218</v>
-      </c>
-      <c r="H37" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="I37" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>150</v>
-      </c>
-      <c r="L37" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>129</v>
-      </c>
-      <c r="M37" s="18">
-        <f t="shared" si="5"/>
-        <v>-10</v>
-      </c>
-      <c r="N37" s="18"/>
-      <c r="O37" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P37" s="18">
-        <f t="shared" si="6"/>
-        <v>23.8</v>
-      </c>
-      <c r="Q37" s="19">
-        <f t="shared" si="11"/>
-        <v>258</v>
-      </c>
-      <c r="R37" s="19"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U37" s="18">
-        <f t="shared" si="8"/>
-        <v>9.1596638655462179</v>
-      </c>
-      <c r="V37" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>19</v>
-      </c>
-      <c r="W37" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>27.2</v>
-      </c>
-      <c r="X37" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>27.6</v>
-      </c>
-      <c r="Y37" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>13</v>
-      </c>
-      <c r="Z37" s="18"/>
-      <c r="AA37" s="18">
-        <f t="shared" si="9"/>
-        <v>46.44</v>
-      </c>
-      <c r="AB37" s="18">
-        <f t="shared" si="10"/>
-        <v>4.2839999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="10">
-        <v>36.363999999999997</v>
-      </c>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10">
-        <v>0</v>
-      </c>
-      <c r="G38" s="10">
-        <v>36.363999999999997</v>
-      </c>
-      <c r="H38" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>1</v>
-      </c>
-      <c r="I38" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L38" s="18">
-        <v>0</v>
-      </c>
-      <c r="M38" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P38" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="19"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U38" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V38" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W38" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X38" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z38" s="18"/>
-      <c r="AA38" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB38" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>5038459</v>
-      </c>
-      <c r="D39" s="10">
-        <v>398</v>
-      </c>
-      <c r="E39" s="10">
-        <v>1</v>
-      </c>
-      <c r="F39" s="10">
-        <v>128</v>
-      </c>
-      <c r="G39" s="10">
-        <v>270</v>
-      </c>
-      <c r="H39" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="I39" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>150</v>
-      </c>
-      <c r="L39" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>140</v>
-      </c>
-      <c r="M39" s="18">
-        <f t="shared" si="5"/>
-        <v>-12</v>
-      </c>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P39" s="18">
-        <f t="shared" si="6"/>
-        <v>25.6</v>
-      </c>
-      <c r="Q39" s="19">
-        <f t="shared" si="11"/>
-        <v>242</v>
-      </c>
-      <c r="R39" s="19"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U39" s="18">
-        <f t="shared" si="8"/>
-        <v>10.546875</v>
-      </c>
-      <c r="V39" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>23.2</v>
-      </c>
-      <c r="W39" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>29.6</v>
-      </c>
-      <c r="X39" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>23.4</v>
-      </c>
-      <c r="Y39" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>19.399999999999999</v>
-      </c>
-      <c r="Z39" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA39" s="18">
-        <f t="shared" si="9"/>
-        <v>43.559999999999995</v>
-      </c>
-      <c r="AB39" s="18">
-        <f t="shared" si="10"/>
-        <v>4.6079999999999997</v>
-      </c>
-    </row>
-    <row r="40" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>5038831</v>
-      </c>
-      <c r="D40" s="10">
-        <v>283</v>
-      </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10">
-        <v>43</v>
-      </c>
-      <c r="G40" s="10">
-        <v>240</v>
-      </c>
-      <c r="H40" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="L40" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>53</v>
-      </c>
-      <c r="M40" s="18">
-        <f t="shared" si="5"/>
-        <v>-10</v>
-      </c>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P40" s="18">
-        <f t="shared" si="6"/>
-        <v>8.6</v>
-      </c>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="18">
-        <f t="shared" si="7"/>
-        <v>27.906976744186046</v>
-      </c>
-      <c r="U40" s="18">
-        <f t="shared" si="8"/>
-        <v>27.906976744186046</v>
-      </c>
-      <c r="V40" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>13.2</v>
-      </c>
-      <c r="W40" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>15.2</v>
-      </c>
-      <c r="X40" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>9.6</v>
-      </c>
-      <c r="Y40" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>11.8</v>
-      </c>
-      <c r="Z40" s="18"/>
-      <c r="AA40" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB40" s="18">
-        <f t="shared" si="10"/>
-        <v>1.5479999999999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>5038855</v>
-      </c>
-      <c r="D41" s="10">
-        <v>195</v>
-      </c>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10">
-        <v>36</v>
-      </c>
-      <c r="G41" s="10">
-        <v>159</v>
-      </c>
-      <c r="H41" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="L41" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>43</v>
-      </c>
-      <c r="M41" s="18">
-        <f t="shared" si="5"/>
-        <v>-7</v>
-      </c>
-      <c r="N41" s="18"/>
-      <c r="O41" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P41" s="18">
-        <f t="shared" si="6"/>
-        <v>7.2</v>
-      </c>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="18"/>
-      <c r="T41" s="18">
-        <f t="shared" si="7"/>
-        <v>22.083333333333332</v>
-      </c>
-      <c r="U41" s="18">
-        <f t="shared" si="8"/>
-        <v>22.083333333333332</v>
-      </c>
-      <c r="V41" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W41" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>6.2</v>
-      </c>
-      <c r="X41" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="Y41" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>9</v>
-      </c>
-      <c r="Z41" s="18"/>
-      <c r="AA41" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB41" s="18">
-        <f t="shared" si="10"/>
-        <v>1.296</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>5038435</v>
-      </c>
-      <c r="D42" s="10">
-        <v>262</v>
-      </c>
-      <c r="E42" s="10">
-        <v>32</v>
-      </c>
-      <c r="F42" s="10">
-        <v>137</v>
-      </c>
-      <c r="G42" s="10">
-        <v>157</v>
-      </c>
-      <c r="H42" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="I42" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>150</v>
-      </c>
-      <c r="L42" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>151</v>
-      </c>
-      <c r="M42" s="18">
-        <f t="shared" si="5"/>
-        <v>-14</v>
-      </c>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>216</v>
-      </c>
-      <c r="P42" s="18">
-        <f t="shared" si="6"/>
-        <v>27.4</v>
-      </c>
-      <c r="Q42" s="19">
-        <f t="shared" si="11"/>
-        <v>175</v>
-      </c>
-      <c r="R42" s="19"/>
-      <c r="S42" s="18"/>
-      <c r="T42" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U42" s="18">
-        <f t="shared" si="8"/>
-        <v>5.7299270072992705</v>
-      </c>
-      <c r="V42" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>32.4</v>
-      </c>
-      <c r="W42" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>24.6</v>
-      </c>
-      <c r="X42" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>20.8</v>
-      </c>
-      <c r="Y42" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>25.4</v>
-      </c>
-      <c r="Z42" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA42" s="18">
-        <f t="shared" si="9"/>
-        <v>31.5</v>
-      </c>
-      <c r="AB42" s="18">
-        <f t="shared" si="10"/>
-        <v>4.9319999999999995</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>5038398</v>
-      </c>
-      <c r="D43" s="10">
-        <v>371</v>
-      </c>
-      <c r="E43" s="10">
-        <v>150</v>
-      </c>
-      <c r="F43" s="10">
-        <v>58</v>
-      </c>
-      <c r="G43" s="10">
-        <v>463</v>
-      </c>
-      <c r="H43" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="I43" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$I,9,0)</f>
-        <v>120</v>
-      </c>
-      <c r="L43" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>66</v>
-      </c>
-      <c r="M43" s="18">
-        <f t="shared" si="5"/>
-        <v>-8</v>
-      </c>
-      <c r="N43" s="18"/>
-      <c r="O43" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P43" s="18">
-        <f t="shared" si="6"/>
-        <v>11.6</v>
-      </c>
-      <c r="Q43" s="19"/>
-      <c r="R43" s="19"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="18">
-        <f t="shared" si="7"/>
-        <v>39.913793103448278</v>
-      </c>
-      <c r="U43" s="18">
-        <f t="shared" si="8"/>
-        <v>39.913793103448278</v>
-      </c>
-      <c r="V43" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>4.8</v>
-      </c>
-      <c r="W43" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>12.8</v>
-      </c>
-      <c r="X43" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>13.2</v>
-      </c>
-      <c r="Y43" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>9.4</v>
-      </c>
-      <c r="Z43" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA43" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB43" s="18">
-        <f t="shared" si="10"/>
-        <v>2.0880000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>9988681</v>
-      </c>
-      <c r="D44" s="10">
-        <v>186</v>
-      </c>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10">
-        <v>41</v>
-      </c>
-      <c r="G44" s="10">
-        <v>145</v>
-      </c>
-      <c r="H44" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="L44" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>42</v>
-      </c>
-      <c r="M44" s="18">
-        <f t="shared" si="5"/>
-        <v>-1</v>
-      </c>
-      <c r="N44" s="18"/>
-      <c r="O44" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P44" s="18">
-        <f t="shared" si="6"/>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="Q44" s="19">
-        <f t="shared" si="11"/>
-        <v>19</v>
-      </c>
-      <c r="R44" s="19"/>
-      <c r="S44" s="18"/>
-      <c r="T44" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U44" s="18">
-        <f t="shared" si="8"/>
-        <v>17.682926829268293</v>
-      </c>
-      <c r="V44" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>12.4</v>
-      </c>
-      <c r="W44" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>5.8</v>
-      </c>
-      <c r="X44" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>7.4</v>
-      </c>
-      <c r="Y44" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>8.6</v>
-      </c>
-      <c r="Z44" s="18"/>
-      <c r="AA44" s="18">
-        <f t="shared" si="9"/>
-        <v>3.42</v>
-      </c>
-      <c r="AB44" s="18">
-        <f t="shared" si="10"/>
-        <v>1.4759999999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" s="9" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>дубль</v>
-      </c>
-      <c r="D45" s="10">
-        <v>59.167999999999999</v>
-      </c>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10">
-        <v>6.6180000000000003</v>
-      </c>
-      <c r="G45" s="10">
-        <v>52.55</v>
-      </c>
-      <c r="H45" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L45" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>5</v>
-      </c>
-      <c r="M45" s="18">
-        <f t="shared" si="5"/>
-        <v>1.6180000000000003</v>
-      </c>
-      <c r="N45" s="18"/>
-      <c r="O45" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P45" s="18">
-        <f t="shared" si="6"/>
-        <v>1.3236000000000001</v>
-      </c>
-      <c r="Q45" s="19"/>
-      <c r="R45" s="19"/>
-      <c r="S45" s="18"/>
-      <c r="T45" s="18">
-        <f t="shared" si="7"/>
-        <v>39.702326987005129</v>
-      </c>
-      <c r="U45" s="18">
-        <f t="shared" si="8"/>
-        <v>39.702326987005129</v>
-      </c>
-      <c r="V45" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>1.3355999999999999</v>
-      </c>
-      <c r="W45" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>1.988</v>
-      </c>
-      <c r="X45" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>2.0207999999999999</v>
-      </c>
-      <c r="Y45" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>0.68840000000000001</v>
-      </c>
-      <c r="Z45" s="18"/>
-      <c r="AA45" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB45" s="18">
-        <f t="shared" si="10"/>
-        <v>1.3236000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>8785198</v>
-      </c>
-      <c r="D46" s="10">
-        <v>80.581999999999994</v>
-      </c>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10">
-        <v>18.98</v>
-      </c>
-      <c r="G46" s="10">
-        <v>61.601999999999997</v>
-      </c>
-      <c r="H46" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L46" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>20.2</v>
-      </c>
-      <c r="M46" s="18">
-        <f t="shared" si="5"/>
-        <v>-1.2199999999999989</v>
-      </c>
-      <c r="N46" s="18"/>
-      <c r="O46" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P46" s="18">
-        <f t="shared" si="6"/>
-        <v>3.7960000000000003</v>
-      </c>
-      <c r="Q46" s="19">
-        <f t="shared" si="11"/>
-        <v>14.318000000000005</v>
-      </c>
-      <c r="R46" s="19"/>
-      <c r="S46" s="18"/>
-      <c r="T46" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U46" s="18">
-        <f t="shared" si="8"/>
-        <v>16.228134878819809</v>
-      </c>
-      <c r="V46" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>3.8764000000000003</v>
-      </c>
-      <c r="W46" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>3.9607999999999999</v>
-      </c>
-      <c r="X46" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>0.71599999999999997</v>
-      </c>
-      <c r="Y46" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z46" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA46" s="18">
-        <f t="shared" si="9"/>
-        <v>14.318000000000005</v>
-      </c>
-      <c r="AB46" s="18">
-        <f t="shared" si="10"/>
-        <v>3.7960000000000003</v>
-      </c>
-    </row>
-    <row r="47" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>8444187</v>
-      </c>
-      <c r="D47" s="10">
-        <v>112</v>
-      </c>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10">
-        <v>68</v>
-      </c>
-      <c r="G47" s="10">
-        <v>42</v>
-      </c>
-      <c r="H47" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="L47" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>70</v>
-      </c>
-      <c r="M47" s="18">
-        <f t="shared" si="5"/>
-        <v>-2</v>
-      </c>
-      <c r="N47" s="18"/>
-      <c r="O47" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>52</v>
-      </c>
-      <c r="P47" s="18">
-        <f t="shared" si="6"/>
-        <v>13.6</v>
-      </c>
-      <c r="Q47" s="19">
-        <f t="shared" si="11"/>
-        <v>178</v>
-      </c>
-      <c r="R47" s="19"/>
-      <c r="S47" s="18"/>
-      <c r="T47" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U47" s="18">
-        <f t="shared" si="8"/>
-        <v>3.0882352941176472</v>
-      </c>
-      <c r="V47" s="18">
+      <c r="V56" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
         <v>8.6</v>
       </c>
-      <c r="W47" s="18">
+      <c r="W56" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>-0.4</v>
-      </c>
-      <c r="X47" s="18">
+        <v>0</v>
+      </c>
+      <c r="X56" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>4.8</v>
-      </c>
-      <c r="Y47" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="Z47" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA47" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="17"/>
+      <c r="AA56" s="17">
         <f t="shared" si="9"/>
-        <v>17.8</v>
-      </c>
-      <c r="AB47" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="17">
         <f t="shared" si="10"/>
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:28" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B48" s="9" t="s">
+    <row r="57" spans="1:29" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C48" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>8444194</v>
-      </c>
-      <c r="D48" s="10">
-        <v>174</v>
-      </c>
-      <c r="E48" s="10">
-        <v>2</v>
-      </c>
-      <c r="F48" s="10">
-        <v>71</v>
-      </c>
-      <c r="G48" s="10">
-        <v>101</v>
-      </c>
-      <c r="H48" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="L48" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>75</v>
-      </c>
-      <c r="M48" s="18">
-        <f t="shared" si="5"/>
-        <v>-4</v>
-      </c>
-      <c r="N48" s="18"/>
-      <c r="O48" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P48" s="18">
-        <f t="shared" si="6"/>
-        <v>14.2</v>
-      </c>
-      <c r="Q48" s="19">
-        <f t="shared" si="11"/>
-        <v>183</v>
-      </c>
-      <c r="R48" s="19"/>
-      <c r="S48" s="18"/>
-      <c r="T48" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U48" s="18">
-        <f t="shared" si="8"/>
-        <v>7.1126760563380289</v>
-      </c>
-      <c r="V48" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>12.6</v>
-      </c>
-      <c r="W48" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>2.6</v>
-      </c>
-      <c r="X48" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>7.4</v>
-      </c>
-      <c r="Y48" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>7.6</v>
-      </c>
-      <c r="Z48" s="18"/>
-      <c r="AA48" s="18">
-        <f t="shared" si="9"/>
-        <v>18.3</v>
-      </c>
-      <c r="AB48" s="18">
-        <f t="shared" si="10"/>
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="49" spans="1:29" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>9988391</v>
-      </c>
-      <c r="D49" s="10">
-        <v>48</v>
-      </c>
-      <c r="E49" s="10">
-        <v>64</v>
-      </c>
-      <c r="F49" s="10">
-        <v>31</v>
-      </c>
-      <c r="G49" s="10">
-        <v>81</v>
-      </c>
-      <c r="H49" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="L49" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>31</v>
-      </c>
-      <c r="M49" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N49" s="18"/>
-      <c r="O49" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>32</v>
-      </c>
-      <c r="P49" s="18">
-        <f t="shared" si="6"/>
-        <v>6.2</v>
-      </c>
-      <c r="Q49" s="19">
-        <f t="shared" si="11"/>
-        <v>11</v>
-      </c>
-      <c r="R49" s="19"/>
-      <c r="S49" s="18"/>
-      <c r="T49" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U49" s="18">
-        <f t="shared" si="8"/>
-        <v>13.064516129032258</v>
-      </c>
-      <c r="V49" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>1</v>
-      </c>
-      <c r="W49" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>3.6</v>
-      </c>
-      <c r="X49" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>7</v>
-      </c>
-      <c r="Y49" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>7</v>
-      </c>
-      <c r="Z49" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA49" s="18">
-        <f t="shared" si="9"/>
-        <v>1.54</v>
-      </c>
-      <c r="AB49" s="18">
-        <f t="shared" si="10"/>
-        <v>0.8680000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:29" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>9988377</v>
-      </c>
-      <c r="D50" s="10">
-        <v>97</v>
-      </c>
-      <c r="E50" s="10">
-        <v>32</v>
-      </c>
-      <c r="F50" s="10">
-        <v>40</v>
-      </c>
-      <c r="G50" s="10">
-        <v>89</v>
-      </c>
-      <c r="H50" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="L50" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>40</v>
-      </c>
-      <c r="M50" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N50" s="18"/>
-      <c r="O50" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>25</v>
-      </c>
-      <c r="P50" s="18">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="Q50" s="19">
-        <f t="shared" si="11"/>
-        <v>46</v>
-      </c>
-      <c r="R50" s="19"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U50" s="18">
-        <f t="shared" si="8"/>
-        <v>11.125</v>
-      </c>
-      <c r="V50" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>5.2</v>
-      </c>
-      <c r="W50" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>7.4</v>
-      </c>
-      <c r="X50" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>7.4</v>
-      </c>
-      <c r="Y50" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>7.6</v>
-      </c>
-      <c r="Z50" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA50" s="18">
-        <f t="shared" si="9"/>
-        <v>6.44</v>
-      </c>
-      <c r="AB50" s="18">
-        <f t="shared" si="10"/>
-        <v>1.1200000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:29" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="9" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>783К798</v>
-      </c>
-      <c r="D51" s="10">
-        <v>333</v>
-      </c>
-      <c r="E51" s="10">
-        <v>72</v>
-      </c>
-      <c r="F51" s="10">
-        <v>123</v>
-      </c>
-      <c r="G51" s="10">
-        <v>210</v>
-      </c>
-      <c r="H51" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.2</v>
-      </c>
-      <c r="L51" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>123</v>
-      </c>
-      <c r="M51" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N51" s="18"/>
-      <c r="O51" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P51" s="18">
-        <f t="shared" si="6"/>
-        <v>24.6</v>
-      </c>
-      <c r="Q51" s="19">
-        <f t="shared" si="11"/>
-        <v>282</v>
-      </c>
-      <c r="R51" s="19"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U51" s="18">
-        <f t="shared" si="8"/>
-        <v>8.5365853658536572</v>
-      </c>
-      <c r="V51" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>31.8</v>
-      </c>
-      <c r="W51" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>13.8</v>
-      </c>
-      <c r="X51" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="Y51" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>13.2</v>
-      </c>
-      <c r="Z51" s="18"/>
-      <c r="AA51" s="18">
-        <f t="shared" si="9"/>
-        <v>56.400000000000006</v>
-      </c>
-      <c r="AB51" s="18">
-        <f t="shared" si="10"/>
-        <v>4.9200000000000008</v>
-      </c>
-    </row>
-    <row r="52" spans="1:29" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C52" s="9" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>дубль798</v>
-      </c>
-      <c r="D52" s="10">
-        <v>154.012</v>
-      </c>
-      <c r="E52" s="10">
-        <v>3.3140000000000001</v>
-      </c>
-      <c r="F52" s="10">
-        <v>15.311999999999999</v>
-      </c>
-      <c r="G52" s="10">
-        <v>138.69999999999999</v>
-      </c>
-      <c r="H52" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L52" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>25</v>
-      </c>
-      <c r="M52" s="18">
-        <f t="shared" si="5"/>
-        <v>-9.6880000000000006</v>
-      </c>
-      <c r="N52" s="18"/>
-      <c r="O52" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P52" s="18">
-        <f t="shared" si="6"/>
-        <v>3.0623999999999998</v>
-      </c>
-      <c r="Q52" s="19"/>
-      <c r="R52" s="19"/>
-      <c r="S52" s="18"/>
-      <c r="T52" s="18">
-        <f t="shared" si="7"/>
-        <v>45.291274817136888</v>
-      </c>
-      <c r="U52" s="18">
-        <f t="shared" si="8"/>
-        <v>45.291274817136888</v>
-      </c>
-      <c r="V52" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>3.8747999999999996</v>
-      </c>
-      <c r="W52" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>1.1103999999999998</v>
-      </c>
-      <c r="X52" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>7.4767999999999999</v>
-      </c>
-      <c r="Y52" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>3.6636000000000002</v>
-      </c>
-      <c r="Z52" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA52" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB52" s="18">
-        <f t="shared" si="10"/>
-        <v>3.0623999999999998</v>
-      </c>
-    </row>
-    <row r="53" spans="1:29" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="9" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>783К801</v>
-      </c>
-      <c r="D53" s="10">
-        <v>158</v>
-      </c>
-      <c r="E53" s="10">
-        <v>58</v>
-      </c>
-      <c r="F53" s="10">
-        <v>75</v>
-      </c>
-      <c r="G53" s="10">
-        <v>123</v>
-      </c>
-      <c r="H53" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.2</v>
-      </c>
-      <c r="L53" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>75</v>
-      </c>
-      <c r="M53" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P53" s="18">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="Q53" s="19">
-        <f t="shared" si="11"/>
-        <v>177</v>
-      </c>
-      <c r="R53" s="19"/>
-      <c r="S53" s="18"/>
-      <c r="T53" s="18">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="U53" s="18">
-        <f t="shared" si="8"/>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="V53" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="W53" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>14</v>
-      </c>
-      <c r="X53" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>12.2</v>
-      </c>
-      <c r="Y53" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>8.6</v>
-      </c>
-      <c r="Z53" s="18"/>
-      <c r="AA53" s="18">
-        <f t="shared" si="9"/>
-        <v>35.4</v>
-      </c>
-      <c r="AB53" s="18">
-        <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:29" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="10">
-        <v>270.7</v>
-      </c>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10">
-        <v>14.747999999999999</v>
-      </c>
-      <c r="G54" s="10">
-        <v>255.952</v>
-      </c>
-      <c r="H54" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L54" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>14</v>
-      </c>
-      <c r="M54" s="18">
-        <f t="shared" si="5"/>
-        <v>0.74799999999999933</v>
-      </c>
-      <c r="N54" s="18"/>
-      <c r="O54" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P54" s="18">
-        <f t="shared" si="6"/>
-        <v>2.9495999999999998</v>
-      </c>
-      <c r="Q54" s="19"/>
-      <c r="R54" s="19"/>
-      <c r="S54" s="18"/>
-      <c r="T54" s="18">
-        <f t="shared" si="7"/>
-        <v>86.775155953349611</v>
-      </c>
-      <c r="U54" s="18">
-        <f t="shared" si="8"/>
-        <v>86.775155953349611</v>
-      </c>
-      <c r="V54" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>1.4567999999999999</v>
-      </c>
-      <c r="W54" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>8.5687999999999995</v>
-      </c>
-      <c r="X54" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>2.1876000000000002</v>
-      </c>
-      <c r="Y54" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>2.4E-2</v>
-      </c>
-      <c r="Z54" s="18" t="str">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Z,26,0)</f>
-        <v>увел продажи</v>
-      </c>
-      <c r="AA54" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB54" s="18">
-        <f t="shared" si="10"/>
-        <v>2.9495999999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:29" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>3534796</v>
-      </c>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10">
-        <v>0</v>
-      </c>
-      <c r="G55" s="10"/>
-      <c r="H55" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="L55" s="18">
-        <v>0</v>
-      </c>
-      <c r="M55" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N55" s="18"/>
-      <c r="O55" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P55" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q55" s="19"/>
-      <c r="R55" s="19"/>
-      <c r="S55" s="18"/>
-      <c r="T55" s="18" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U55" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V55" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W55" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X55" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y55" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z55" s="18"/>
-      <c r="AA55" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB55" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:29" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="9">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
-        <v>6819</v>
-      </c>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10">
-        <v>0</v>
-      </c>
-      <c r="G56" s="10"/>
-      <c r="H56" s="5">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
-        <v>0.3</v>
-      </c>
-      <c r="L56" s="18">
-        <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
-        <v>28</v>
-      </c>
-      <c r="M56" s="18">
-        <f t="shared" si="5"/>
-        <v>-28</v>
-      </c>
-      <c r="N56" s="18"/>
-      <c r="O56" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Q,17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P56" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q56" s="19"/>
-      <c r="R56" s="19"/>
-      <c r="S56" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T56" s="18" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U56" s="18" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V56" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
-        <v>8.6</v>
-      </c>
-      <c r="W56" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X56" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y56" s="18">
-        <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z56" s="18"/>
-      <c r="AA56" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB56" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:29" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" s="9">
+      <c r="C57" s="8">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$C,3,0)</f>
         <v>7216</v>
       </c>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10">
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9">
         <v>133</v>
       </c>
-      <c r="G57" s="10"/>
-      <c r="H57" s="5">
+      <c r="G57" s="9"/>
+      <c r="H57">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$H,8,0)</f>
         <v>0.7</v>
       </c>
-      <c r="I57" s="5"/>
-      <c r="L57" s="18">
+      <c r="L57" s="17">
         <f>VLOOKUP(A:A,[2]TDSheet!$A:$B,2,0)</f>
         <v>4</v>
       </c>
-      <c r="M57" s="18">
+      <c r="M57" s="17">
         <f t="shared" si="5"/>
         <v>129</v>
       </c>
-      <c r="N57" s="21"/>
-      <c r="O57" s="18">
-        <v>0</v>
-      </c>
-      <c r="P57" s="18">
+      <c r="N57" s="17"/>
+      <c r="O57" s="17">
+        <v>0</v>
+      </c>
+      <c r="P57" s="17">
         <f t="shared" si="6"/>
         <v>26.6</v>
       </c>
-      <c r="Q57" s="19"/>
-      <c r="R57" s="19"/>
-      <c r="S57" s="22"/>
-      <c r="T57" s="18">
+      <c r="Q57" s="25"/>
+      <c r="R57" s="18"/>
+      <c r="S57" s="17"/>
+      <c r="T57" s="17">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U57" s="18">
+      <c r="U57" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V57" s="18">
+      <c r="V57" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$W,23,0)</f>
         <v>0</v>
       </c>
-      <c r="W57" s="18">
+      <c r="W57" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$X,24,0)</f>
         <v>20.2</v>
       </c>
-      <c r="X57" s="18">
+      <c r="X57" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$Y,25,0)</f>
         <v>12</v>
       </c>
-      <c r="Y57" s="18">
+      <c r="Y57" s="17">
         <f>VLOOKUP(A:A,[1]TDSheet!$A:$P,16,0)</f>
         <v>23.6</v>
       </c>
-      <c r="Z57" s="18"/>
-      <c r="AA57" s="18">
+      <c r="Z57" s="17"/>
+      <c r="AA57" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AB57" s="18">
+      <c r="AB57" s="17">
         <f t="shared" si="10"/>
         <v>18.62</v>
       </c>
-      <c r="AC57" s="21"/>
+      <c r="AC57" s="17"/>
     </row>
     <row r="58" spans="1:29" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C58" s="9"/>
-      <c r="Y58" s="18"/>
+      <c r="C58" s="8"/>
+      <c r="Y58" s="17"/>
     </row>
     <row r="59" spans="1:29" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Y59" s="18"/>
+      <c r="Y59" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A8:AB57" xr:uid="{9B75763C-1588-4024-86F1-BC4E5243ED93}"/>
